--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_2_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/5_five_bus_radial_grid_1ph_ynyn_MP_pf_sc_results_2_branch.xlsx
@@ -646,49 +646,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.282962610066685</v>
+        <v>4.282962610066692</v>
       </c>
       <c r="C2">
-        <v>4.282962610066685</v>
+        <v>4.282962610066692</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.277811204449899</v>
+        <v>9.277811204449907</v>
       </c>
       <c r="F2">
-        <v>148.3661769510661</v>
+        <v>148.3661769510664</v>
       </c>
       <c r="G2">
-        <v>148.3661769510661</v>
+        <v>148.3661769510664</v>
       </c>
       <c r="H2">
-        <v>28.61627979050433</v>
+        <v>28.61627979050436</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>32.46847082824983</v>
+        <v>32.46847082824975</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-77.77984579421408</v>
+        <v>-77.77984579421407</v>
       </c>
       <c r="M2">
         <v>102.2201542057786</v>
       </c>
       <c r="N2">
-        <v>0.2917056037382958</v>
+        <v>0.2917056037382951</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-29.17137735526041</v>
+        <v>-29.17137735526048</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -843,127 +843,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.709154423746197</v>
+        <v>3.709154423744982</v>
       </c>
       <c r="D2">
-        <v>3.709154423746191</v>
+        <v>3.709154423744979</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.709154423746193</v>
+        <v>3.70915442374498</v>
       </c>
       <c r="G2">
-        <v>3.709154423746191</v>
+        <v>3.709154423744978</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42.82962610031516</v>
+        <v>42.82962610030114</v>
       </c>
       <c r="J2">
-        <v>42.8296261003151</v>
+        <v>42.8296261003011</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>42.82962610031511</v>
+        <v>42.82962610030111</v>
       </c>
       <c r="M2">
-        <v>42.8296261003151</v>
+        <v>42.82962610030109</v>
       </c>
       <c r="N2">
-        <v>-1.563194052542763E-14</v>
+        <v>-2.08425873672372E-14</v>
       </c>
       <c r="O2">
-        <v>30.17661447772734</v>
+        <v>30.17661447772222</v>
       </c>
       <c r="P2">
-        <v>-15.86847458187111</v>
+        <v>-15.86847458187513</v>
       </c>
       <c r="Q2">
-        <v>-1.5631940525427E-14</v>
+        <v>-5.210646841809228E-15</v>
       </c>
       <c r="R2">
-        <v>-23.02254452973994</v>
+        <v>-23.02254452973952</v>
       </c>
       <c r="S2">
-        <v>23.02254452985859</v>
+        <v>23.02254452985794</v>
       </c>
       <c r="T2">
-        <v>-5.210646841807091E-15</v>
+        <v>1.042129368361836E-14</v>
       </c>
       <c r="U2">
-        <v>3.130989834145738</v>
+        <v>3.13098983418737</v>
       </c>
       <c r="V2">
-        <v>13.10324558048884</v>
+        <v>13.10324558045216</v>
       </c>
       <c r="W2">
-        <v>1.904117332321756E-27</v>
+        <v>-5.210646841809327E-15</v>
       </c>
       <c r="X2">
-        <v>4.986127873181712</v>
+        <v>4.986127873134766</v>
       </c>
       <c r="Y2">
-        <v>-4.986127873161449</v>
+        <v>-4.986127873130087</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-167.7798457937229</v>
+        <v>-167.7798457937528</v>
       </c>
       <c r="AB2">
-        <v>12.22015420626987</v>
+        <v>12.22015420623991</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>12.22015420626988</v>
+        <v>12.22015420623994</v>
       </c>
       <c r="AE2">
-        <v>-167.7798457937229</v>
+        <v>-167.7798457937528</v>
       </c>
       <c r="AF2">
-        <v>1.100000023834231</v>
+        <v>1.10000002383429</v>
       </c>
       <c r="AG2">
-        <v>0.7083556674756124</v>
+        <v>0.7083556674758256</v>
       </c>
       <c r="AH2">
-        <v>0.4804898682207091</v>
+        <v>0.480489868220393</v>
       </c>
       <c r="AI2">
-        <v>1.100000023834231</v>
+        <v>1.10000002383429</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119158659</v>
+        <v>0.5500000119158041</v>
       </c>
       <c r="AK2">
-        <v>0.5500000119184737</v>
+        <v>0.5500000119184835</v>
       </c>
       <c r="AL2">
-        <v>-6.989567673226516E-12</v>
+        <v>5.352460154071194E-13</v>
       </c>
       <c r="AM2">
-        <v>-161.8562887546769</v>
+        <v>-161.8562887546276</v>
       </c>
       <c r="AN2">
-        <v>152.6722796269069</v>
+        <v>152.6722796269628</v>
       </c>
       <c r="AO2">
-        <v>-6.979164657278612E-12</v>
+        <v>5.452158490297898E-13</v>
       </c>
       <c r="AP2">
-        <v>179.9999999998726</v>
+        <v>179.999999999954</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999999818</v>
+        <v>-179.9999999999593</v>
       </c>
     </row>
   </sheetData>
@@ -1115,127 +1115,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.763086650584325</v>
+        <v>1.7630866505842</v>
       </c>
       <c r="D2">
-        <v>1.763086650584326</v>
+        <v>1.7630866505842</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.763086650584325</v>
+        <v>1.763086650584199</v>
       </c>
       <c r="G2">
-        <v>1.763086650584325</v>
+        <v>1.7630866505842</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>20.35837104638991</v>
+        <v>20.35837104638847</v>
       </c>
       <c r="J2">
-        <v>20.35837104638992</v>
+        <v>20.35837104638847</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20.35837104638992</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="M2">
-        <v>20.35837104638992</v>
+        <v>20.35837104638847</v>
       </c>
       <c r="N2">
-        <v>7.815970262743617E-15</v>
+        <v>2.084525959993511E-29</v>
       </c>
       <c r="O2">
-        <v>19.0760556007679</v>
+        <v>19.0760556007627</v>
       </c>
       <c r="P2">
-        <v>-0.3008693307207994</v>
+        <v>-0.3008693307267443</v>
       </c>
       <c r="Q2">
-        <v>-2.605323420914861E-15</v>
+        <v>-2.605323420914377E-15</v>
       </c>
       <c r="R2">
-        <v>-17.45964880793389</v>
+        <v>-17.45964880792891</v>
       </c>
       <c r="S2">
-        <v>1.917276123554825</v>
+        <v>1.917276123560533</v>
       </c>
       <c r="T2">
-        <v>5.210646841828031E-15</v>
+        <v>-5.210646841828691E-15</v>
       </c>
       <c r="U2">
-        <v>3.991912765037412</v>
+        <v>3.991912765039885</v>
       </c>
       <c r="V2">
-        <v>15.21845990328519</v>
+        <v>15.21845990328567</v>
       </c>
       <c r="W2">
-        <v>-5.210646841828514E-15</v>
+        <v>7.815970262743025E-15</v>
       </c>
       <c r="X2">
-        <v>-2.157912776814145</v>
+        <v>-2.157912776816865</v>
       </c>
       <c r="Y2">
-        <v>-13.38445991506192</v>
+        <v>-13.38445991506267</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-149.9129785515108</v>
+        <v>-149.9129785515271</v>
       </c>
       <c r="AB2">
-        <v>30.08702144848187</v>
+        <v>30.0870214484656</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>30.08702144848185</v>
+        <v>30.08702144846559</v>
       </c>
       <c r="AE2">
-        <v>-149.9129785515108</v>
+        <v>-149.9129785515271</v>
       </c>
       <c r="AF2">
-        <v>1.100000023838402</v>
+        <v>1.100000023838388</v>
       </c>
       <c r="AG2">
-        <v>0.9573094133258242</v>
+        <v>0.957309413325667</v>
       </c>
       <c r="AH2">
-        <v>0.747674441885505</v>
+        <v>0.7476744418855878</v>
       </c>
       <c r="AI2">
-        <v>1.100000023838402</v>
+        <v>1.100000023838388</v>
       </c>
       <c r="AJ2">
-        <v>0.8641406624622873</v>
+        <v>0.8641406624621228</v>
       </c>
       <c r="AK2">
-        <v>0.6641535346104747</v>
+        <v>0.664153534610598</v>
       </c>
       <c r="AL2">
-        <v>-5.315912890881542E-12</v>
+        <v>2.292125016693008E-13</v>
       </c>
       <c r="AM2">
-        <v>-138.0936484456504</v>
+        <v>-138.0936484456564</v>
       </c>
       <c r="AN2">
-        <v>121.2196128903309</v>
+        <v>121.219612890337</v>
       </c>
       <c r="AO2">
-        <v>-5.315232614965016E-12</v>
+        <v>2.255771306429001E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.8672784203968</v>
+        <v>-142.8672784204023</v>
       </c>
       <c r="AQ2">
-        <v>128.2389811279505</v>
+        <v>128.2389811279577</v>
       </c>
     </row>
   </sheetData>
@@ -1387,127 +1387,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.763086650584325</v>
+        <v>1.7630866505842</v>
       </c>
       <c r="D2">
-        <v>1.763086650584326</v>
+        <v>1.763086650584199</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.763086650584325</v>
+        <v>1.763086650584199</v>
       </c>
       <c r="G2">
-        <v>1.763086650584325</v>
+        <v>1.763086650584199</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>20.35837104638991</v>
+        <v>20.35837104638847</v>
       </c>
       <c r="J2">
-        <v>20.35837104638992</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>20.35837104638992</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="M2">
-        <v>20.35837104638992</v>
+        <v>20.35837104638846</v>
       </c>
       <c r="N2">
-        <v>7.815970262743617E-15</v>
+        <v>-1.014104385531662E-29</v>
       </c>
       <c r="O2">
-        <v>19.0760556007679</v>
+        <v>19.0760556007627</v>
       </c>
       <c r="P2">
-        <v>-0.3008693307207994</v>
+        <v>-0.300869330726749</v>
       </c>
       <c r="Q2">
-        <v>-2.605323420914861E-15</v>
+        <v>-5.210646841828691E-15</v>
       </c>
       <c r="R2">
-        <v>-17.45964880793389</v>
+        <v>-17.4596488079289</v>
       </c>
       <c r="S2">
-        <v>1.917276123554825</v>
+        <v>1.917276123560534</v>
       </c>
       <c r="T2">
-        <v>5.210646841828031E-15</v>
+        <v>2.605323420914345E-15</v>
       </c>
       <c r="U2">
-        <v>3.991912765037412</v>
+        <v>3.991912765039883</v>
       </c>
       <c r="V2">
-        <v>15.21845990328519</v>
+        <v>15.21845990328566</v>
       </c>
       <c r="W2">
-        <v>-5.210646841828514E-15</v>
+        <v>-2.063816097669572E-29</v>
       </c>
       <c r="X2">
-        <v>-2.157912776814145</v>
+        <v>-2.157912776816863</v>
       </c>
       <c r="Y2">
-        <v>-13.38445991506192</v>
+        <v>-13.38445991506266</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-149.9129785515108</v>
+        <v>-149.9129785515271</v>
       </c>
       <c r="AB2">
-        <v>30.08702144848187</v>
+        <v>30.08702144846558</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>30.08702144848185</v>
+        <v>30.08702144846559</v>
       </c>
       <c r="AE2">
-        <v>-149.9129785515108</v>
+        <v>-149.9129785515271</v>
       </c>
       <c r="AF2">
-        <v>1.100000023838402</v>
+        <v>1.100000023838388</v>
       </c>
       <c r="AG2">
-        <v>0.9573094133258242</v>
+        <v>0.9573094133256668</v>
       </c>
       <c r="AH2">
-        <v>0.747674441885505</v>
+        <v>0.747674441885588</v>
       </c>
       <c r="AI2">
-        <v>1.100000023838402</v>
+        <v>1.100000023838388</v>
       </c>
       <c r="AJ2">
-        <v>0.8641406624622873</v>
+        <v>0.8641406624621224</v>
       </c>
       <c r="AK2">
-        <v>0.6641535346104747</v>
+        <v>0.6641535346105982</v>
       </c>
       <c r="AL2">
-        <v>-5.315912890881542E-12</v>
+        <v>2.230199168757245E-13</v>
       </c>
       <c r="AM2">
-        <v>-138.0936484456504</v>
+        <v>-138.0936484456564</v>
       </c>
       <c r="AN2">
-        <v>121.2196128903309</v>
+        <v>121.219612890337</v>
       </c>
       <c r="AO2">
-        <v>-5.315232614965016E-12</v>
+        <v>2.269352648089301E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.8672784203968</v>
+        <v>-142.8672784204023</v>
       </c>
       <c r="AQ2">
-        <v>128.2389811279505</v>
+        <v>128.2389811279577</v>
       </c>
     </row>
   </sheetData>
@@ -1659,127 +1659,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.119085825227508</v>
+        <v>3.119085825228931</v>
       </c>
       <c r="D2">
-        <v>3.119085825227507</v>
+        <v>3.119085825228931</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.119085825227508</v>
+        <v>3.11908582522893</v>
       </c>
       <c r="G2">
-        <v>3.119085825227508</v>
+        <v>3.119085825228932</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>36.01610081641296</v>
+        <v>36.01610081642939</v>
       </c>
       <c r="J2">
-        <v>36.01610081641295</v>
+        <v>36.01610081642939</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>36.01610081641295</v>
+        <v>36.01610081642938</v>
       </c>
       <c r="M2">
-        <v>36.01610081641296</v>
+        <v>36.0161008164294</v>
       </c>
       <c r="N2">
-        <v>-7.105427357632411E-15</v>
+        <v>9.473903143508832E-15</v>
       </c>
       <c r="O2">
-        <v>26.59966124763405</v>
+        <v>26.59966124765506</v>
       </c>
       <c r="P2">
-        <v>-7.173399904881161</v>
+        <v>-7.17339990489539</v>
       </c>
       <c r="Q2">
-        <v>-8.929666608750226E-29</v>
+        <v>-9.473903143508784E-15</v>
       </c>
       <c r="R2">
-        <v>-16.88653057631013</v>
+        <v>-16.88653057632229</v>
       </c>
       <c r="S2">
-        <v>16.88653057620524</v>
+        <v>16.88653057622834</v>
       </c>
       <c r="T2">
-        <v>-4.736951571754744E-15</v>
+        <v>8.841887154708932E-29</v>
       </c>
       <c r="U2">
-        <v>-0.5158635800600754</v>
+        <v>-0.5158635800632787</v>
       </c>
       <c r="V2">
-        <v>11.99572538444129</v>
+        <v>11.9957253844309</v>
       </c>
       <c r="W2">
-        <v>-4.73695157175488E-15</v>
+        <v>-4.736951571754505E-15</v>
       </c>
       <c r="X2">
-        <v>6.255794482082362</v>
+        <v>6.255794482090781</v>
       </c>
       <c r="Y2">
-        <v>-6.255794482419094</v>
+        <v>-6.255794482403475</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-159.6723164477184</v>
+        <v>-159.6723164477259</v>
       </c>
       <c r="AB2">
-        <v>20.32768355227432</v>
+        <v>20.32768355226677</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>20.32768355227434</v>
+        <v>20.32768355226676</v>
       </c>
       <c r="AE2">
-        <v>-159.6723164477184</v>
+        <v>-159.6723164477259</v>
       </c>
       <c r="AF2">
-        <v>1.000000000004408</v>
+        <v>1.00000000000431</v>
       </c>
       <c r="AG2">
-        <v>0.7386880424043644</v>
+        <v>0.7386880424046126</v>
       </c>
       <c r="AH2">
-        <v>0.3880750091710275</v>
+        <v>0.3880750091708057</v>
       </c>
       <c r="AI2">
-        <v>1.000000000004408</v>
+        <v>1.000000000004309</v>
       </c>
       <c r="AJ2">
-        <v>0.5000000000016988</v>
+        <v>0.5000000000018686</v>
       </c>
       <c r="AK2">
-        <v>0.5000000000022158</v>
+        <v>0.5000000000024385</v>
       </c>
       <c r="AL2">
-        <v>-1.096935601959864E-12</v>
+        <v>5.347350603249968E-13</v>
       </c>
       <c r="AM2">
-        <v>-160.7833494395864</v>
+        <v>-160.7833494396</v>
       </c>
       <c r="AN2">
-        <v>141.2069528723597</v>
+        <v>141.2069528724241</v>
       </c>
       <c r="AO2">
-        <v>-1.080087481136573E-12</v>
+        <v>5.44293057080252E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999994575</v>
+        <v>-179.9999999994768</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999994073</v>
+        <v>179.9999999994719</v>
       </c>
     </row>
   </sheetData>
@@ -1931,127 +1931,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.119085825227508</v>
+        <v>3.119085825228931</v>
       </c>
       <c r="D2">
-        <v>3.119085825227507</v>
+        <v>3.119085825228931</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.119085825227508</v>
+        <v>3.11908582522893</v>
       </c>
       <c r="G2">
-        <v>3.119085825227508</v>
+        <v>3.119085825228932</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>36.01610081641296</v>
+        <v>36.01610081642939</v>
       </c>
       <c r="J2">
-        <v>36.01610081641295</v>
+        <v>36.01610081642939</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>36.01610081641295</v>
+        <v>36.01610081642938</v>
       </c>
       <c r="M2">
-        <v>36.01610081641296</v>
+        <v>36.0161008164294</v>
       </c>
       <c r="N2">
-        <v>-7.105427357632411E-15</v>
+        <v>9.473903143508832E-15</v>
       </c>
       <c r="O2">
-        <v>26.59966124763405</v>
+        <v>26.59966124765506</v>
       </c>
       <c r="P2">
-        <v>-7.173399904881161</v>
+        <v>-7.17339990489539</v>
       </c>
       <c r="Q2">
-        <v>-8.929666608750226E-29</v>
+        <v>-9.473903143508784E-15</v>
       </c>
       <c r="R2">
-        <v>-16.88653057631013</v>
+        <v>-16.88653057632229</v>
       </c>
       <c r="S2">
-        <v>16.88653057620524</v>
+        <v>16.88653057622834</v>
       </c>
       <c r="T2">
-        <v>-4.736951571754744E-15</v>
+        <v>8.841887154708932E-29</v>
       </c>
       <c r="U2">
-        <v>-0.5158635800600754</v>
+        <v>-0.5158635800632787</v>
       </c>
       <c r="V2">
-        <v>11.99572538444129</v>
+        <v>11.9957253844309</v>
       </c>
       <c r="W2">
-        <v>-4.73695157175488E-15</v>
+        <v>-4.736951571754505E-15</v>
       </c>
       <c r="X2">
-        <v>6.255794482082362</v>
+        <v>6.255794482090781</v>
       </c>
       <c r="Y2">
-        <v>-6.255794482419094</v>
+        <v>-6.255794482403475</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-159.6723164477184</v>
+        <v>-159.6723164477259</v>
       </c>
       <c r="AB2">
-        <v>20.32768355227432</v>
+        <v>20.32768355226677</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>20.32768355227434</v>
+        <v>20.32768355226676</v>
       </c>
       <c r="AE2">
-        <v>-159.6723164477184</v>
+        <v>-159.6723164477259</v>
       </c>
       <c r="AF2">
-        <v>1.000000000004408</v>
+        <v>1.00000000000431</v>
       </c>
       <c r="AG2">
-        <v>0.7386880424043644</v>
+        <v>0.7386880424046126</v>
       </c>
       <c r="AH2">
-        <v>0.3880750091710275</v>
+        <v>0.3880750091708057</v>
       </c>
       <c r="AI2">
-        <v>1.000000000004408</v>
+        <v>1.000000000004309</v>
       </c>
       <c r="AJ2">
-        <v>0.5000000000016988</v>
+        <v>0.5000000000018686</v>
       </c>
       <c r="AK2">
-        <v>0.5000000000022158</v>
+        <v>0.5000000000024385</v>
       </c>
       <c r="AL2">
-        <v>-1.096935601959864E-12</v>
+        <v>5.347350603249968E-13</v>
       </c>
       <c r="AM2">
-        <v>-160.7833494395864</v>
+        <v>-160.7833494396</v>
       </c>
       <c r="AN2">
-        <v>141.2069528723597</v>
+        <v>141.2069528724241</v>
       </c>
       <c r="AO2">
-        <v>-1.080087481136573E-12</v>
+        <v>5.44293057080252E-13</v>
       </c>
       <c r="AP2">
-        <v>-179.9999999994575</v>
+        <v>-179.9999999994768</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999994073</v>
+        <v>179.9999999994719</v>
       </c>
     </row>
   </sheetData>
@@ -2203,127 +2203,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.518298438952745</v>
+        <v>1.518298438953095</v>
       </c>
       <c r="D2">
-        <v>1.518298438952746</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.518298438952745</v>
+        <v>1.518298438953095</v>
       </c>
       <c r="G2">
-        <v>1.518298438952745</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>17.53180024879112</v>
+        <v>17.53180024879516</v>
       </c>
       <c r="J2">
-        <v>17.53180024879113</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>17.53180024879112</v>
+        <v>17.53180024879516</v>
       </c>
       <c r="M2">
-        <v>17.53180024879113</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="N2">
-        <v>-2.960594732344156E-15</v>
+        <v>-5.921189464689116E-16</v>
       </c>
       <c r="O2">
-        <v>15.39322071799903</v>
+        <v>15.39322071800312</v>
       </c>
       <c r="P2">
-        <v>0.7360136868477104</v>
+        <v>0.7360136868429361</v>
       </c>
       <c r="Q2">
-        <v>4.144832625282456E-15</v>
+        <v>1.993098364954682E-29</v>
       </c>
       <c r="R2">
-        <v>-13.09167888902598</v>
+        <v>-13.091678889029</v>
       </c>
       <c r="S2">
-        <v>1.565528142125378</v>
+        <v>1.565528142131214</v>
       </c>
       <c r="T2">
-        <v>-9.4739031435029E-15</v>
+        <v>4.736951571751132E-15</v>
       </c>
       <c r="U2">
-        <v>2.313527558712144</v>
+        <v>2.313527558708346</v>
       </c>
       <c r="V2">
-        <v>11.93279478711575</v>
+        <v>11.93279478711935</v>
       </c>
       <c r="W2">
-        <v>1.988375208090783E-28</v>
+        <v>-4.736951571751134E-15</v>
       </c>
       <c r="X2">
-        <v>-0.9534417621294544</v>
+        <v>-0.9534417621250336</v>
       </c>
       <c r="Y2">
-        <v>-10.57270899053308</v>
+        <v>-10.57270899053605</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-146.7238138638783</v>
+        <v>-146.723813863879</v>
       </c>
       <c r="AB2">
-        <v>33.27618613611445</v>
+        <v>33.27618613611371</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>33.27618613611444</v>
+        <v>33.2761861361137</v>
       </c>
       <c r="AE2">
-        <v>-146.7238138638783</v>
+        <v>-146.723813863879</v>
       </c>
       <c r="AF2">
-        <v>1.000000000003668</v>
+        <v>1.000000000003617</v>
       </c>
       <c r="AG2">
-        <v>0.887878353024368</v>
+        <v>0.8878783530243616</v>
       </c>
       <c r="AH2">
-        <v>0.6819306459126562</v>
+        <v>0.6819306459126869</v>
       </c>
       <c r="AI2">
-        <v>1.000000000003668</v>
+        <v>1.000000000003617</v>
       </c>
       <c r="AJ2">
-        <v>0.7487167006142769</v>
+        <v>0.7487167006142579</v>
       </c>
       <c r="AK2">
-        <v>0.6096342800272869</v>
+        <v>0.6096342800273626</v>
       </c>
       <c r="AL2">
-        <v>2.751256296441333E-12</v>
+        <v>2.401203026090395E-13</v>
       </c>
       <c r="AM2">
-        <v>-138.1765060860218</v>
+        <v>-138.1765060860386</v>
       </c>
       <c r="AN2">
-        <v>119.7466591084755</v>
+        <v>119.7466591084986</v>
       </c>
       <c r="AO2">
-        <v>2.748615392021541E-12</v>
+        <v>2.410751360586704E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.5584264978932</v>
+        <v>-142.5584264979142</v>
       </c>
       <c r="AQ2">
-        <v>131.6989175372223</v>
+        <v>131.6989175372502</v>
       </c>
     </row>
   </sheetData>
@@ -2475,127 +2475,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1.518298438952745</v>
+        <v>1.518298438953095</v>
       </c>
       <c r="D2">
-        <v>1.518298438952746</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.518298438952745</v>
+        <v>1.518298438953095</v>
       </c>
       <c r="G2">
-        <v>1.518298438952745</v>
+        <v>1.518298438953096</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>17.53180024879112</v>
+        <v>17.53180024879516</v>
       </c>
       <c r="J2">
-        <v>17.53180024879113</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>17.53180024879112</v>
+        <v>17.53180024879516</v>
       </c>
       <c r="M2">
-        <v>17.53180024879113</v>
+        <v>17.53180024879517</v>
       </c>
       <c r="N2">
-        <v>-2.960594732344156E-15</v>
+        <v>-5.921189464689116E-16</v>
       </c>
       <c r="O2">
-        <v>15.39322071799903</v>
+        <v>15.39322071800312</v>
       </c>
       <c r="P2">
-        <v>0.7360136868477104</v>
+        <v>0.7360136868429361</v>
       </c>
       <c r="Q2">
-        <v>4.144832625282456E-15</v>
+        <v>1.993098364954682E-29</v>
       </c>
       <c r="R2">
-        <v>-13.09167888902598</v>
+        <v>-13.091678889029</v>
       </c>
       <c r="S2">
-        <v>1.565528142125378</v>
+        <v>1.565528142131214</v>
       </c>
       <c r="T2">
-        <v>-9.4739031435029E-15</v>
+        <v>4.736951571751132E-15</v>
       </c>
       <c r="U2">
-        <v>2.313527558712144</v>
+        <v>2.313527558708346</v>
       </c>
       <c r="V2">
-        <v>11.93279478711575</v>
+        <v>11.93279478711935</v>
       </c>
       <c r="W2">
-        <v>1.988375208090783E-28</v>
+        <v>-4.736951571751134E-15</v>
       </c>
       <c r="X2">
-        <v>-0.9534417621294544</v>
+        <v>-0.9534417621250336</v>
       </c>
       <c r="Y2">
-        <v>-10.57270899053308</v>
+        <v>-10.57270899053605</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-146.7238138638783</v>
+        <v>-146.723813863879</v>
       </c>
       <c r="AB2">
-        <v>33.27618613611445</v>
+        <v>33.27618613611371</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>33.27618613611444</v>
+        <v>33.2761861361137</v>
       </c>
       <c r="AE2">
-        <v>-146.7238138638783</v>
+        <v>-146.723813863879</v>
       </c>
       <c r="AF2">
-        <v>1.000000000003668</v>
+        <v>1.000000000003617</v>
       </c>
       <c r="AG2">
-        <v>0.887878353024368</v>
+        <v>0.8878783530243616</v>
       </c>
       <c r="AH2">
-        <v>0.6819306459126562</v>
+        <v>0.6819306459126869</v>
       </c>
       <c r="AI2">
-        <v>1.000000000003668</v>
+        <v>1.000000000003617</v>
       </c>
       <c r="AJ2">
-        <v>0.7487167006142769</v>
+        <v>0.7487167006142579</v>
       </c>
       <c r="AK2">
-        <v>0.6096342800272869</v>
+        <v>0.6096342800273626</v>
       </c>
       <c r="AL2">
-        <v>2.751256296441333E-12</v>
+        <v>2.401203026090395E-13</v>
       </c>
       <c r="AM2">
-        <v>-138.1765060860218</v>
+        <v>-138.1765060860386</v>
       </c>
       <c r="AN2">
-        <v>119.7466591084755</v>
+        <v>119.7466591084986</v>
       </c>
       <c r="AO2">
-        <v>2.748615392021541E-12</v>
+        <v>2.410751360586704E-13</v>
       </c>
       <c r="AP2">
-        <v>-142.5584264978932</v>
+        <v>-142.5584264979142</v>
       </c>
       <c r="AQ2">
-        <v>131.6989175372223</v>
+        <v>131.6989175372502</v>
       </c>
     </row>
   </sheetData>
@@ -2747,16 +2747,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.150115884156516</v>
+        <v>4.150115884449223</v>
       </c>
       <c r="C2">
-        <v>0.001307688482546056</v>
+        <v>0.00130768848204236</v>
       </c>
       <c r="D2">
-        <v>0.001307688482545665</v>
+        <v>0.00130768848204207</v>
       </c>
       <c r="E2">
-        <v>4.149403056925948</v>
+        <v>4.149403057218605</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -2765,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>47.92141045771812</v>
+        <v>47.92141046109801</v>
       </c>
       <c r="I2">
-        <v>0.01509988594828278</v>
+        <v>0.01509988594246659</v>
       </c>
       <c r="J2">
-        <v>0.01509988594827825</v>
+        <v>0.01509988594246325</v>
       </c>
       <c r="K2">
-        <v>47.91317943784905</v>
+        <v>47.91317944122837</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -2783,52 +2783,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>27.19116802648402</v>
+        <v>27.19116803031878</v>
       </c>
       <c r="O2">
-        <v>0.01384375202539629</v>
+        <v>0.01384375202133934</v>
       </c>
       <c r="P2">
-        <v>-0.01236984081412779</v>
+        <v>-0.01236984081031253</v>
       </c>
       <c r="Q2">
-        <v>3.084967657459626E-10</v>
+        <v>3.097520142531103E-10</v>
       </c>
       <c r="R2">
-        <v>1.649977340750067E-09</v>
+        <v>1.649978677794953E-09</v>
       </c>
       <c r="S2">
-        <v>-6.143769469203074E-09</v>
+        <v>-6.14375075023659E-09</v>
       </c>
       <c r="T2">
-        <v>15.20531856887977</v>
+        <v>15.2053185710236</v>
       </c>
       <c r="U2">
-        <v>0.0003364921161722653</v>
+        <v>0.0003364921157014145</v>
       </c>
       <c r="V2">
-        <v>-0.01151725764283178</v>
+        <v>-0.01151725763381842</v>
       </c>
       <c r="W2">
-        <v>-3.697415478057705E-10</v>
+        <v>-3.679302973075826E-10</v>
       </c>
       <c r="X2">
-        <v>-3.311288107552381E-09</v>
+        <v>-3.311264762689313E-09</v>
       </c>
       <c r="Y2">
-        <v>-1.188429968196629E-09</v>
+        <v>-1.188436345794273E-09</v>
       </c>
       <c r="Z2">
-        <v>-57.37178928772604</v>
+        <v>-57.3717892940281</v>
       </c>
       <c r="AA2">
-        <v>-114.3324158490127</v>
+        <v>-114.3324158382698</v>
       </c>
       <c r="AB2">
-        <v>-114.3324158490402</v>
+        <v>-114.3324158382854</v>
       </c>
       <c r="AC2">
-        <v>122.6433476770584</v>
+        <v>122.6433476707465</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -2837,40 +2837,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6501025958293946</v>
+        <v>0.650102595875221</v>
       </c>
       <c r="AH2">
-        <v>0.9170824818895968</v>
+        <v>0.9170824819734873</v>
       </c>
       <c r="AI2">
-        <v>1.119312077401033</v>
+        <v>1.119312077240402</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.8726123021385497</v>
+        <v>0.8726123021113025</v>
       </c>
       <c r="AL2">
-        <v>1.475971874238363</v>
+        <v>1.475971874113954</v>
       </c>
       <c r="AM2">
-        <v>-28.15784080480957</v>
+        <v>-28.15784081111256</v>
       </c>
       <c r="AN2">
-        <v>-112.9400344628234</v>
+        <v>-112.9400344536202</v>
       </c>
       <c r="AO2">
-        <v>108.6234392878127</v>
+        <v>108.6234392850183</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-138.2768647797111</v>
+        <v>-138.2768647707442</v>
       </c>
       <c r="AR2">
-        <v>116.1844690778667</v>
+        <v>116.1844690754271</v>
       </c>
     </row>
   </sheetData>
@@ -3022,16 +3022,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.150115884156516</v>
+        <v>4.150115884449222</v>
       </c>
       <c r="C2">
-        <v>0.001307688482546056</v>
+        <v>0.001307688482042462</v>
       </c>
       <c r="D2">
-        <v>0.001307688482545665</v>
+        <v>0.00130768848204248</v>
       </c>
       <c r="E2">
-        <v>4.149403056925948</v>
+        <v>4.149403057218604</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3040,16 +3040,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>47.92141045771812</v>
+        <v>47.921410461098</v>
       </c>
       <c r="I2">
-        <v>0.01509988594828278</v>
+        <v>0.01509988594246777</v>
       </c>
       <c r="J2">
-        <v>0.01509988594827825</v>
+        <v>0.01509988594246798</v>
       </c>
       <c r="K2">
-        <v>47.91317943784905</v>
+        <v>47.91317944122836</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3058,52 +3058,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>27.19116802648402</v>
+        <v>27.19116803031876</v>
       </c>
       <c r="O2">
-        <v>0.01384375202539629</v>
+        <v>0.0138437520213405</v>
       </c>
       <c r="P2">
-        <v>-0.01236984081412779</v>
+        <v>-0.01236984081032596</v>
       </c>
       <c r="Q2">
-        <v>3.084967657459626E-10</v>
+        <v>3.097777671106537E-10</v>
       </c>
       <c r="R2">
-        <v>1.649977340750067E-09</v>
+        <v>1.649972507525044E-09</v>
       </c>
       <c r="S2">
-        <v>-6.143769469203074E-09</v>
+        <v>-6.143716294528324E-09</v>
       </c>
       <c r="T2">
-        <v>15.20531856887977</v>
+        <v>15.2053185710236</v>
       </c>
       <c r="U2">
-        <v>0.0003364921161722653</v>
+        <v>0.0003364921156985678</v>
       </c>
       <c r="V2">
-        <v>-0.01151725764283178</v>
+        <v>-0.01151725763381176</v>
       </c>
       <c r="W2">
-        <v>-3.697415478057705E-10</v>
+        <v>-3.679215252909823E-10</v>
       </c>
       <c r="X2">
-        <v>-3.311288107552381E-09</v>
+        <v>-3.31127026467013E-09</v>
       </c>
       <c r="Y2">
-        <v>-1.188429968196629E-09</v>
+        <v>-1.188427194234166E-09</v>
       </c>
       <c r="Z2">
-        <v>-57.37178928772604</v>
+        <v>-57.37178929402812</v>
       </c>
       <c r="AA2">
-        <v>-114.3324158490127</v>
+        <v>-114.3324158382579</v>
       </c>
       <c r="AB2">
-        <v>-114.3324158490402</v>
+        <v>-114.3324158382378</v>
       </c>
       <c r="AC2">
-        <v>122.6433476770584</v>
+        <v>122.6433476707465</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3112,40 +3112,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.6501025958293946</v>
+        <v>0.6501025958752206</v>
       </c>
       <c r="AH2">
-        <v>0.9170824818895968</v>
+        <v>0.9170824819734872</v>
       </c>
       <c r="AI2">
-        <v>1.119312077401033</v>
+        <v>1.119312077240402</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.8726123021385497</v>
+        <v>0.8726123021113026</v>
       </c>
       <c r="AL2">
-        <v>1.475971874238363</v>
+        <v>1.475971874113954</v>
       </c>
       <c r="AM2">
-        <v>-28.15784080480957</v>
+        <v>-28.15784081111255</v>
       </c>
       <c r="AN2">
-        <v>-112.9400344628234</v>
+        <v>-112.9400344536202</v>
       </c>
       <c r="AO2">
-        <v>108.6234392878127</v>
+        <v>108.6234392850183</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-138.2768647797111</v>
+        <v>-138.2768647707442</v>
       </c>
       <c r="AR2">
-        <v>116.1844690778667</v>
+        <v>116.1844690754271</v>
       </c>
     </row>
   </sheetData>
@@ -3297,16 +3297,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.259987556237371</v>
+        <v>1.259987556270372</v>
       </c>
       <c r="C2">
-        <v>0.0003970181222488954</v>
+        <v>0.0003970181220780942</v>
       </c>
       <c r="D2">
-        <v>0.0003970181222489093</v>
+        <v>0.000397018122078199</v>
       </c>
       <c r="E2">
-        <v>1.259771139764835</v>
+        <v>1.25977113979783</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3315,16 +3315,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>14.5490830953845</v>
+        <v>14.54908309576556</v>
       </c>
       <c r="I2">
-        <v>0.00458437039507119</v>
+        <v>0.004584370393098948</v>
       </c>
       <c r="J2">
-        <v>0.004584370395071351</v>
+        <v>0.004584370393100159</v>
       </c>
       <c r="K2">
-        <v>14.54658413321099</v>
+        <v>14.54658413359198</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3333,52 +3333,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>10.44072245393943</v>
+        <v>10.4407224544876</v>
       </c>
       <c r="O2">
-        <v>0.004639096644342601</v>
+        <v>0.004639096642170153</v>
       </c>
       <c r="P2">
-        <v>-0.003769400342288119</v>
+        <v>-0.003769400341476479</v>
       </c>
       <c r="Q2">
-        <v>-7.935116622294974</v>
+        <v>-7.935116622710492</v>
       </c>
       <c r="R2">
-        <v>6.842589528093782E-10</v>
+        <v>6.842575104276174E-10</v>
       </c>
       <c r="S2">
-        <v>-1.558416982156546E-09</v>
+        <v>-1.558419104314635E-09</v>
       </c>
       <c r="T2">
-        <v>9.34012301053288</v>
+        <v>9.34012301102071</v>
       </c>
       <c r="U2">
-        <v>-0.001063278738745943</v>
+        <v>-0.001063278739351866</v>
       </c>
       <c r="V2">
-        <v>-0.00342694161657679</v>
+        <v>-0.003426941613914007</v>
       </c>
       <c r="W2">
-        <v>-7.935116625724198</v>
+        <v>-7.935116626139713</v>
       </c>
       <c r="X2">
-        <v>-1.143565726646232E-09</v>
+        <v>-1.143562455997152E-09</v>
       </c>
       <c r="Y2">
-        <v>-1.512437890732325E-10</v>
+        <v>-1.512400244656869E-10</v>
       </c>
       <c r="Z2">
-        <v>-48.740263662224</v>
+        <v>-48.74026366392469</v>
       </c>
       <c r="AA2">
-        <v>-105.7008902235264</v>
+        <v>-105.7008902081703</v>
       </c>
       <c r="AB2">
-        <v>-105.7008902235335</v>
+        <v>-105.7008902081968</v>
       </c>
       <c r="AC2">
-        <v>131.2748733025605</v>
+        <v>131.2748733008499</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3387,40 +3387,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9628650605236372</v>
+        <v>0.962865060548855</v>
       </c>
       <c r="AH2">
-        <v>1.038177140577603</v>
+        <v>1.038177140591862</v>
       </c>
       <c r="AI2">
-        <v>1.111241091242308</v>
+        <v>1.111241091198393</v>
       </c>
       <c r="AJ2">
-        <v>0.7714491213827978</v>
+        <v>0.7714491214029893</v>
       </c>
       <c r="AK2">
-        <v>1.035324491806451</v>
+        <v>1.035324491812154</v>
       </c>
       <c r="AL2">
-        <v>1.216410836943163</v>
+        <v>1.21641083690306</v>
       </c>
       <c r="AM2">
-        <v>-6.924897552168047</v>
+        <v>-6.924897553876513</v>
       </c>
       <c r="AN2">
-        <v>-118.6100874871913</v>
+        <v>-118.6100874847879</v>
       </c>
       <c r="AO2">
-        <v>116.5745799767652</v>
+        <v>116.5745799760834</v>
       </c>
       <c r="AP2">
-        <v>-3.725126685053678</v>
+        <v>-3.725126686764178</v>
       </c>
       <c r="AQ2">
-        <v>-125.2375227440031</v>
+        <v>-125.2375227416983</v>
       </c>
       <c r="AR2">
-        <v>119.4112336957558</v>
+        <v>119.4112336951555</v>
       </c>
     </row>
   </sheetData>
@@ -3491,49 +3491,49 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.282962610066681</v>
+        <v>4.282962610066682</v>
       </c>
       <c r="C2">
-        <v>4.282962610066681</v>
+        <v>4.282962610066682</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9.27781120444989</v>
+        <v>9.277811204449897</v>
       </c>
       <c r="F2">
-        <v>148.366176951066</v>
+        <v>148.3661769510661</v>
       </c>
       <c r="G2">
-        <v>148.366176951066</v>
+        <v>148.3661769510661</v>
       </c>
       <c r="H2">
-        <v>28.61627979050424</v>
+        <v>28.6162797905042</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>32.46847082824999</v>
+        <v>32.46847082824993</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-77.77984579421411</v>
+        <v>-77.77984579421414</v>
       </c>
       <c r="M2">
         <v>102.2201542057786</v>
       </c>
       <c r="N2">
-        <v>0.2917056037382966</v>
+        <v>0.291705603738296</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-29.17137735526021</v>
+        <v>-29.17137735526025</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -3688,16 +3688,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.259987556237371</v>
+        <v>1.259987556270371</v>
       </c>
       <c r="C2">
-        <v>0.0003970181222488954</v>
+        <v>0.0003970181220781651</v>
       </c>
       <c r="D2">
-        <v>0.0003970181222489093</v>
+        <v>0.0003970181220783687</v>
       </c>
       <c r="E2">
-        <v>1.259771139764835</v>
+        <v>1.25977113979783</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3706,16 +3706,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>14.5490830953845</v>
+        <v>14.54908309576555</v>
       </c>
       <c r="I2">
-        <v>0.00458437039507119</v>
+        <v>0.004584370393099767</v>
       </c>
       <c r="J2">
-        <v>0.004584370395071351</v>
+        <v>0.004584370393102119</v>
       </c>
       <c r="K2">
-        <v>14.54658413321099</v>
+        <v>14.54658413359198</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3724,52 +3724,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>10.44072245393943</v>
+        <v>10.44072245448761</v>
       </c>
       <c r="O2">
-        <v>0.004639096644342601</v>
+        <v>0.004639096642170644</v>
       </c>
       <c r="P2">
-        <v>-0.003769400342288119</v>
+        <v>-0.003769400341479422</v>
       </c>
       <c r="Q2">
-        <v>-7.935116622294974</v>
+        <v>-7.935116622710499</v>
       </c>
       <c r="R2">
-        <v>6.842589528093782E-10</v>
+        <v>6.842582178302455E-10</v>
       </c>
       <c r="S2">
-        <v>-1.558416982156546E-09</v>
+        <v>-1.558409840450554E-09</v>
       </c>
       <c r="T2">
-        <v>9.34012301053288</v>
+        <v>9.340123011020697</v>
       </c>
       <c r="U2">
-        <v>-0.001063278738745943</v>
+        <v>-0.001063278739353534</v>
       </c>
       <c r="V2">
-        <v>-0.00342694161657679</v>
+        <v>-0.003426941613914008</v>
       </c>
       <c r="W2">
-        <v>-7.935116625724198</v>
+        <v>-7.935116626139703</v>
       </c>
       <c r="X2">
-        <v>-1.143565726646232E-09</v>
+        <v>-1.143561454582962E-09</v>
       </c>
       <c r="Y2">
-        <v>-1.512437890732325E-10</v>
+        <v>-1.512447240276411E-10</v>
       </c>
       <c r="Z2">
-        <v>-48.740263662224</v>
+        <v>-48.74026366392462</v>
       </c>
       <c r="AA2">
-        <v>-105.7008902235264</v>
+        <v>-105.7008902081521</v>
       </c>
       <c r="AB2">
-        <v>-105.7008902235335</v>
+        <v>-105.7008902081746</v>
       </c>
       <c r="AC2">
-        <v>131.2748733025605</v>
+        <v>131.27487330085</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -3778,40 +3778,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9628650605236372</v>
+        <v>0.962865060548855</v>
       </c>
       <c r="AH2">
-        <v>1.038177140577603</v>
+        <v>1.038177140591862</v>
       </c>
       <c r="AI2">
-        <v>1.111241091242308</v>
+        <v>1.111241091198393</v>
       </c>
       <c r="AJ2">
-        <v>0.7714491213827978</v>
+        <v>0.7714491214029892</v>
       </c>
       <c r="AK2">
-        <v>1.035324491806451</v>
+        <v>1.035324491812154</v>
       </c>
       <c r="AL2">
-        <v>1.216410836943163</v>
+        <v>1.21641083690306</v>
       </c>
       <c r="AM2">
-        <v>-6.924897552168047</v>
+        <v>-6.924897553876512</v>
       </c>
       <c r="AN2">
-        <v>-118.6100874871913</v>
+        <v>-118.6100874847879</v>
       </c>
       <c r="AO2">
-        <v>116.5745799767652</v>
+        <v>116.5745799760834</v>
       </c>
       <c r="AP2">
-        <v>-3.725126685053678</v>
+        <v>-3.72512668676419</v>
       </c>
       <c r="AQ2">
-        <v>-125.2375227440031</v>
+        <v>-125.2375227416983</v>
       </c>
       <c r="AR2">
-        <v>119.4112336957558</v>
+        <v>119.4112336951555</v>
       </c>
     </row>
   </sheetData>
@@ -3963,16 +3963,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.826503590209353</v>
+        <v>2.826503590419481</v>
       </c>
       <c r="C2">
-        <v>0.001514726916395076</v>
+        <v>0.001514726916047462</v>
       </c>
       <c r="D2">
-        <v>0.00151472691639298</v>
+        <v>0.001514726916046854</v>
       </c>
       <c r="E2">
-        <v>2.826014553940519</v>
+        <v>2.826014554150611</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -3981,16 +3981,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>32.63765217345627</v>
+        <v>32.63765217588262</v>
       </c>
       <c r="I2">
-        <v>0.01749055985858938</v>
+        <v>0.01749055985457548</v>
       </c>
       <c r="J2">
-        <v>0.01749055985856518</v>
+        <v>0.01749055985456846</v>
       </c>
       <c r="K2">
-        <v>32.63200526902718</v>
+        <v>32.63200527145311</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -3999,52 +3999,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>24.21629158552039</v>
+        <v>24.21629158912262</v>
       </c>
       <c r="O2">
-        <v>0.01474207730294907</v>
+        <v>0.01474207729993648</v>
       </c>
       <c r="P2">
-        <v>-0.01341929221375706</v>
+        <v>-0.01341929221076509</v>
       </c>
       <c r="Q2">
-        <v>-9.641019054802215E-11</v>
+        <v>-9.785305727235071E-11</v>
       </c>
       <c r="R2">
-        <v>-7.914572718897496E-10</v>
+        <v>-7.9144593822015E-10</v>
       </c>
       <c r="S2">
-        <v>-8.089694737199178E-09</v>
+        <v>-8.089685923842335E-09</v>
       </c>
       <c r="T2">
-        <v>7.041002540157399</v>
+        <v>7.041002541206193</v>
       </c>
       <c r="U2">
-        <v>-0.00150003566889033</v>
+        <v>-0.001500035667264867</v>
       </c>
       <c r="V2">
-        <v>-0.01266678629034683</v>
+        <v>-0.01266678628505598</v>
       </c>
       <c r="W2">
-        <v>1.357681622988383E-11</v>
+        <v>1.238778469621154E-11</v>
       </c>
       <c r="X2">
-        <v>-5.109522621703065E-09</v>
+        <v>-5.109526340956228E-09</v>
       </c>
       <c r="Y2">
-        <v>8.958853476258784E-10</v>
+        <v>8.958847718314874E-10</v>
       </c>
       <c r="Z2">
-        <v>-40.47982360144594</v>
+        <v>-40.47982360509456</v>
       </c>
       <c r="AA2">
-        <v>-111.6296754787477</v>
+        <v>-111.6296754764873</v>
       </c>
       <c r="AB2">
-        <v>-111.6296754787583</v>
+        <v>-111.6296754764714</v>
       </c>
       <c r="AC2">
-        <v>139.5492395119679</v>
+        <v>139.5492395083094</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4053,40 +4053,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7727004813135351</v>
+        <v>0.7727004813710439</v>
       </c>
       <c r="AH2">
-        <v>0.8472111076465261</v>
+        <v>0.8472111076601879</v>
       </c>
       <c r="AI2">
-        <v>1.055044340500205</v>
+        <v>1.055044340409253</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.9475300847488727</v>
+        <v>0.94753008469165</v>
       </c>
       <c r="AL2">
-        <v>1.491564952146088</v>
+        <v>1.491564952092233</v>
       </c>
       <c r="AM2">
-        <v>-24.26778174265319</v>
+        <v>-24.26778174629869</v>
       </c>
       <c r="AN2">
-        <v>-117.4396389060159</v>
+        <v>-117.439638898682</v>
       </c>
       <c r="AO2">
-        <v>111.717969610303</v>
+        <v>111.7179696070204</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-149.355373888698</v>
+        <v>-149.3553738855857</v>
       </c>
       <c r="AR2">
-        <v>123.1301085605432</v>
+        <v>123.130108558438</v>
       </c>
     </row>
   </sheetData>
@@ -4238,16 +4238,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>2.826503590209353</v>
+        <v>2.826503590419481</v>
       </c>
       <c r="C2">
-        <v>0.001514726916395076</v>
+        <v>0.001514726916047462</v>
       </c>
       <c r="D2">
-        <v>0.00151472691639298</v>
+        <v>0.001514726916046854</v>
       </c>
       <c r="E2">
-        <v>2.826014553940519</v>
+        <v>2.826014554150611</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4256,16 +4256,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>32.63765217345627</v>
+        <v>32.63765217588262</v>
       </c>
       <c r="I2">
-        <v>0.01749055985858938</v>
+        <v>0.01749055985457548</v>
       </c>
       <c r="J2">
-        <v>0.01749055985856518</v>
+        <v>0.01749055985456846</v>
       </c>
       <c r="K2">
-        <v>32.63200526902718</v>
+        <v>32.63200527145311</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4274,52 +4274,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>24.21629158552039</v>
+        <v>24.21629158912262</v>
       </c>
       <c r="O2">
-        <v>0.01474207730294907</v>
+        <v>0.01474207729993648</v>
       </c>
       <c r="P2">
-        <v>-0.01341929221375706</v>
+        <v>-0.01341929221076509</v>
       </c>
       <c r="Q2">
-        <v>-9.641019054802215E-11</v>
+        <v>-9.785305727235071E-11</v>
       </c>
       <c r="R2">
-        <v>-7.914572718897496E-10</v>
+        <v>-7.9144593822015E-10</v>
       </c>
       <c r="S2">
-        <v>-8.089694737199178E-09</v>
+        <v>-8.089685923842335E-09</v>
       </c>
       <c r="T2">
-        <v>7.041002540157399</v>
+        <v>7.041002541206193</v>
       </c>
       <c r="U2">
-        <v>-0.00150003566889033</v>
+        <v>-0.001500035667264867</v>
       </c>
       <c r="V2">
-        <v>-0.01266678629034683</v>
+        <v>-0.01266678628505598</v>
       </c>
       <c r="W2">
-        <v>1.357681622988383E-11</v>
+        <v>1.238778469621154E-11</v>
       </c>
       <c r="X2">
-        <v>-5.109522621703065E-09</v>
+        <v>-5.109526340956228E-09</v>
       </c>
       <c r="Y2">
-        <v>8.958853476258784E-10</v>
+        <v>8.958847718314874E-10</v>
       </c>
       <c r="Z2">
-        <v>-40.47982360144594</v>
+        <v>-40.47982360509456</v>
       </c>
       <c r="AA2">
-        <v>-111.6296754787477</v>
+        <v>-111.6296754764873</v>
       </c>
       <c r="AB2">
-        <v>-111.6296754787583</v>
+        <v>-111.6296754764714</v>
       </c>
       <c r="AC2">
-        <v>139.5492395119679</v>
+        <v>139.5492395083094</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4328,40 +4328,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.7727004813135351</v>
+        <v>0.7727004813710439</v>
       </c>
       <c r="AH2">
-        <v>0.8472111076465261</v>
+        <v>0.8472111076601879</v>
       </c>
       <c r="AI2">
-        <v>1.055044340500205</v>
+        <v>1.055044340409253</v>
       </c>
       <c r="AJ2">
         <v>0</v>
       </c>
       <c r="AK2">
-        <v>0.9475300847488727</v>
+        <v>0.94753008469165</v>
       </c>
       <c r="AL2">
-        <v>1.491564952146088</v>
+        <v>1.491564952092233</v>
       </c>
       <c r="AM2">
-        <v>-24.26778174265319</v>
+        <v>-24.26778174629869</v>
       </c>
       <c r="AN2">
-        <v>-117.4396389060159</v>
+        <v>-117.439638898682</v>
       </c>
       <c r="AO2">
-        <v>111.717969610303</v>
+        <v>111.7179696070204</v>
       </c>
       <c r="AP2">
         <v>0</v>
       </c>
       <c r="AQ2">
-        <v>-149.355373888698</v>
+        <v>-149.3553738855857</v>
       </c>
       <c r="AR2">
-        <v>123.1301085605432</v>
+        <v>123.130108558438</v>
       </c>
     </row>
   </sheetData>
@@ -4513,16 +4513,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.035889633774533</v>
+        <v>1.035889633801501</v>
       </c>
       <c r="C2">
-        <v>0.0005551345896488956</v>
+        <v>0.0005551345894948618</v>
       </c>
       <c r="D2">
-        <v>0.0005551345896489594</v>
+        <v>0.0005551345894949231</v>
       </c>
       <c r="E2">
-        <v>1.035710406122682</v>
+        <v>1.035710406149644</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4531,16 +4531,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>11.96142317820939</v>
+        <v>11.96142317852079</v>
       </c>
       <c r="I2">
-        <v>0.006410142095405246</v>
+        <v>0.006410142093626617</v>
       </c>
       <c r="J2">
-        <v>0.006410142095405984</v>
+        <v>0.006410142093627325</v>
       </c>
       <c r="K2">
-        <v>11.95935363554854</v>
+        <v>11.95935363585987</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4549,52 +4549,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>8.614323076631116</v>
+        <v>8.614323077080783</v>
       </c>
       <c r="O2">
-        <v>0.006036631536636395</v>
+        <v>0.00603663153499311</v>
       </c>
       <c r="P2">
-        <v>-0.004065329098613016</v>
+        <v>-0.00406532909782008</v>
       </c>
       <c r="Q2">
-        <v>-5.363480226970625</v>
+        <v>-5.363480227250081</v>
       </c>
       <c r="R2">
-        <v>4.31743275633582E-10</v>
+        <v>4.317422907668621E-10</v>
       </c>
       <c r="S2">
-        <v>-2.350333383972517E-09</v>
+        <v>-2.350331582949642E-09</v>
       </c>
       <c r="T2">
-        <v>6.312848364182017</v>
+        <v>6.312848364510065</v>
       </c>
       <c r="U2">
-        <v>-0.000472412987530018</v>
+        <v>-0.0004724129876457486</v>
       </c>
       <c r="V2">
-        <v>-0.00507894708310489</v>
+        <v>-0.005078947081142262</v>
       </c>
       <c r="W2">
-        <v>-5.363480229301629</v>
+        <v>-5.363480229581072</v>
       </c>
       <c r="X2">
-        <v>-1.834913421687811E-09</v>
+        <v>-1.834911128240687E-09</v>
       </c>
       <c r="Y2">
-        <v>2.286824028065009E-10</v>
+        <v>2.286794065684778E-10</v>
       </c>
       <c r="Z2">
-        <v>-43.36332196078656</v>
+        <v>-43.36332196219436</v>
       </c>
       <c r="AA2">
-        <v>-114.5131738380897</v>
+        <v>-114.5131738335601</v>
       </c>
       <c r="AB2">
-        <v>-114.5131738381041</v>
+        <v>-114.5131738335485</v>
       </c>
       <c r="AC2">
-        <v>136.6657411526273</v>
+        <v>136.6657411512097</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4603,40 +4603,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8928555332448905</v>
+        <v>0.8928555332681805</v>
       </c>
       <c r="AH2">
-        <v>0.9446106203975893</v>
+        <v>0.9446106204055246</v>
       </c>
       <c r="AI2">
-        <v>1.014888974492891</v>
+        <v>1.014888974458165</v>
       </c>
       <c r="AJ2">
-        <v>0.6342405042362602</v>
+        <v>0.6342405042527943</v>
       </c>
       <c r="AK2">
-        <v>0.9425752861117402</v>
+        <v>0.9425752861083261</v>
       </c>
       <c r="AL2">
-        <v>1.180796373404805</v>
+        <v>1.180796373375345</v>
       </c>
       <c r="AM2">
-        <v>-7.128181816750366</v>
+        <v>-7.12818181816457</v>
       </c>
       <c r="AN2">
-        <v>-118.9878906746481</v>
+        <v>-118.9878906724234</v>
       </c>
       <c r="AO2">
-        <v>116.812084436155</v>
+        <v>116.8120844353612</v>
       </c>
       <c r="AP2">
-        <v>1.665741165083333</v>
+        <v>1.665741163665625</v>
       </c>
       <c r="AQ2">
-        <v>-130.1934967156515</v>
+        <v>-130.1934967136848</v>
       </c>
       <c r="AR2">
-        <v>121.0088117774464</v>
+        <v>121.0088117767831</v>
       </c>
     </row>
   </sheetData>
@@ -4788,16 +4788,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.035889633774533</v>
+        <v>1.035889633801501</v>
       </c>
       <c r="C2">
-        <v>0.0005551345896488956</v>
+        <v>0.0005551345894948618</v>
       </c>
       <c r="D2">
-        <v>0.0005551345896489594</v>
+        <v>0.0005551345894949231</v>
       </c>
       <c r="E2">
-        <v>1.035710406122682</v>
+        <v>1.035710406149644</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -4806,16 +4806,16 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>11.96142317820939</v>
+        <v>11.96142317852079</v>
       </c>
       <c r="I2">
-        <v>0.006410142095405246</v>
+        <v>0.006410142093626617</v>
       </c>
       <c r="J2">
-        <v>0.006410142095405984</v>
+        <v>0.006410142093627325</v>
       </c>
       <c r="K2">
-        <v>11.95935363554854</v>
+        <v>11.95935363585987</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -4824,52 +4824,52 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>8.614323076631116</v>
+        <v>8.614323077080783</v>
       </c>
       <c r="O2">
-        <v>0.006036631536636395</v>
+        <v>0.00603663153499311</v>
       </c>
       <c r="P2">
-        <v>-0.004065329098613016</v>
+        <v>-0.00406532909782008</v>
       </c>
       <c r="Q2">
-        <v>-5.363480226970625</v>
+        <v>-5.363480227250081</v>
       </c>
       <c r="R2">
-        <v>4.31743275633582E-10</v>
+        <v>4.317422907668621E-10</v>
       </c>
       <c r="S2">
-        <v>-2.350333383972517E-09</v>
+        <v>-2.350331582949642E-09</v>
       </c>
       <c r="T2">
-        <v>6.312848364182017</v>
+        <v>6.312848364510065</v>
       </c>
       <c r="U2">
-        <v>-0.000472412987530018</v>
+        <v>-0.0004724129876457486</v>
       </c>
       <c r="V2">
-        <v>-0.00507894708310489</v>
+        <v>-0.005078947081142262</v>
       </c>
       <c r="W2">
-        <v>-5.363480229301629</v>
+        <v>-5.363480229581072</v>
       </c>
       <c r="X2">
-        <v>-1.834913421687811E-09</v>
+        <v>-1.834911128240687E-09</v>
       </c>
       <c r="Y2">
-        <v>2.286824028065009E-10</v>
+        <v>2.286794065684778E-10</v>
       </c>
       <c r="Z2">
-        <v>-43.36332196078656</v>
+        <v>-43.36332196219436</v>
       </c>
       <c r="AA2">
-        <v>-114.5131738380897</v>
+        <v>-114.5131738335601</v>
       </c>
       <c r="AB2">
-        <v>-114.5131738381041</v>
+        <v>-114.5131738335485</v>
       </c>
       <c r="AC2">
-        <v>136.6657411526273</v>
+        <v>136.6657411512097</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -4878,40 +4878,40 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.8928555332448905</v>
+        <v>0.8928555332681805</v>
       </c>
       <c r="AH2">
-        <v>0.9446106203975893</v>
+        <v>0.9446106204055246</v>
       </c>
       <c r="AI2">
-        <v>1.014888974492891</v>
+        <v>1.014888974458165</v>
       </c>
       <c r="AJ2">
-        <v>0.6342405042362602</v>
+        <v>0.6342405042527943</v>
       </c>
       <c r="AK2">
-        <v>0.9425752861117402</v>
+        <v>0.9425752861083261</v>
       </c>
       <c r="AL2">
-        <v>1.180796373404805</v>
+        <v>1.180796373375345</v>
       </c>
       <c r="AM2">
-        <v>-7.128181816750366</v>
+        <v>-7.12818181816457</v>
       </c>
       <c r="AN2">
-        <v>-118.9878906746481</v>
+        <v>-118.9878906724234</v>
       </c>
       <c r="AO2">
-        <v>116.812084436155</v>
+        <v>116.8120844353612</v>
       </c>
       <c r="AP2">
-        <v>1.665741165083333</v>
+        <v>1.665741163665625</v>
       </c>
       <c r="AQ2">
-        <v>-130.1934967156515</v>
+        <v>-130.1934967136848</v>
       </c>
       <c r="AR2">
-        <v>121.0088117774464</v>
+        <v>121.0088117767831</v>
       </c>
     </row>
   </sheetData>
@@ -5063,106 +5063,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001143871124319383</v>
+        <v>0.001143871123997529</v>
       </c>
       <c r="C2">
-        <v>5.026871232749402</v>
+        <v>5.026871232850098</v>
       </c>
       <c r="D2">
-        <v>2.972832707237637</v>
+        <v>2.972832707453473</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.026925725046478</v>
+        <v>5.026925725146896</v>
       </c>
       <c r="G2">
-        <v>2.971978874584844</v>
+        <v>2.971978874800944</v>
       </c>
       <c r="H2">
-        <v>0.01320828603088072</v>
+        <v>0.01320828602716426</v>
       </c>
       <c r="I2">
-        <v>58.04530918818906</v>
+        <v>58.0453091893518</v>
       </c>
       <c r="J2">
-        <v>34.32731527558748</v>
+        <v>34.32731527807974</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>58.04593841103678</v>
+        <v>58.0459384121963</v>
       </c>
       <c r="M2">
-        <v>34.31745606534881</v>
+        <v>34.31745606784413</v>
       </c>
       <c r="N2">
-        <v>-0.0002505547693010971</v>
+        <v>-0.0002505547703392135</v>
       </c>
       <c r="O2">
-        <v>31.94042916143862</v>
+        <v>31.94042916514979</v>
       </c>
       <c r="P2">
-        <v>-0.2508696044269373</v>
+        <v>-0.2508696020939283</v>
       </c>
       <c r="Q2">
-        <v>-3.438412630865273E-09</v>
+        <v>-3.438436899634398E-09</v>
       </c>
       <c r="R2">
-        <v>2.306976120386154E-10</v>
+        <v>2.354842301838077E-10</v>
       </c>
       <c r="S2">
-        <v>1.419868632159606E-10</v>
+        <v>1.560596762269125E-10</v>
       </c>
       <c r="T2">
-        <v>-0.01290413922523335</v>
+        <v>-0.01290413921960348</v>
       </c>
       <c r="U2">
-        <v>7.953445883863187</v>
+        <v>7.9534458818846</v>
       </c>
       <c r="V2">
-        <v>16.03313910159848</v>
+        <v>16.0331391062981</v>
       </c>
       <c r="W2">
-        <v>-3.44294323270769E-09</v>
+        <v>-3.442937840958936E-09</v>
       </c>
       <c r="X2">
-        <v>-1.120163922878213E-10</v>
+        <v>-1.52096465942494E-10</v>
       </c>
       <c r="Y2">
-        <v>-7.194849109134476E-11</v>
+        <v>-5.239022367429415E-11</v>
       </c>
       <c r="Z2">
-        <v>82.8682366066229</v>
+        <v>82.86823661498073</v>
       </c>
       <c r="AA2">
-        <v>175.5922528829084</v>
+        <v>175.592252878299</v>
       </c>
       <c r="AB2">
-        <v>41.15861450991542</v>
+        <v>41.15861451669438</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-4.394724257727977</v>
+        <v>-4.394724262341205</v>
       </c>
       <c r="AE2">
-        <v>-138.8560581246315</v>
+        <v>-138.8560581178478</v>
       </c>
       <c r="AG2">
-        <v>0.9771571746118858</v>
+        <v>0.9771571744622</v>
       </c>
       <c r="AH2">
-        <v>0.5670703897192441</v>
+        <v>0.5670703897616897</v>
       </c>
       <c r="AI2">
-        <v>0.4671236746561608</v>
+        <v>0.4671236747580724</v>
       </c>
       <c r="AJ2">
-        <v>1.312059303119413</v>
+        <v>1.312059303014113</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -5171,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-8.244114005362498</v>
+        <v>-8.244114002097458</v>
       </c>
       <c r="AN2">
-        <v>-170.424970466132</v>
+        <v>-170.4249704756444</v>
       </c>
       <c r="AO2">
-        <v>132.0550451212195</v>
+        <v>132.0550451194005</v>
       </c>
       <c r="AP2">
-        <v>-12.52501517096528</v>
+        <v>-12.52501517175904</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -5338,106 +5338,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.001143871124319383</v>
+        <v>0.001143871123998953</v>
       </c>
       <c r="C2">
-        <v>5.026871232749402</v>
+        <v>5.026871232850097</v>
       </c>
       <c r="D2">
-        <v>2.972832707237637</v>
+        <v>2.97283270745347</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>5.026925725046478</v>
+        <v>5.026925725146896</v>
       </c>
       <c r="G2">
-        <v>2.971978874584844</v>
+        <v>2.971978874800937</v>
       </c>
       <c r="H2">
-        <v>0.01320828603088072</v>
+        <v>0.01320828602718071</v>
       </c>
       <c r="I2">
-        <v>58.04530918818906</v>
+        <v>58.0453091893518</v>
       </c>
       <c r="J2">
-        <v>34.32731527558748</v>
+        <v>34.3273152780797</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>58.04593841103678</v>
+        <v>58.0459384121963</v>
       </c>
       <c r="M2">
-        <v>34.31745606534881</v>
+        <v>34.31745606784405</v>
       </c>
       <c r="N2">
-        <v>-0.0002505547693010971</v>
+        <v>-0.0002505547703601964</v>
       </c>
       <c r="O2">
-        <v>31.94042916143862</v>
+        <v>31.94042916514978</v>
       </c>
       <c r="P2">
-        <v>-0.2508696044269373</v>
+        <v>-0.2508696020939342</v>
       </c>
       <c r="Q2">
-        <v>-3.438412630865273E-09</v>
+        <v>-3.438416002173963E-09</v>
       </c>
       <c r="R2">
-        <v>2.306976120386154E-10</v>
+        <v>2.355188323320086E-10</v>
       </c>
       <c r="S2">
-        <v>1.419868632159606E-10</v>
+        <v>1.560467798585104E-10</v>
       </c>
       <c r="T2">
-        <v>-0.01290413922523335</v>
+        <v>-0.01290413921961915</v>
       </c>
       <c r="U2">
-        <v>7.953445883863187</v>
+        <v>7.953445881884559</v>
       </c>
       <c r="V2">
-        <v>16.03313910159848</v>
+        <v>16.03313910629809</v>
       </c>
       <c r="W2">
-        <v>-3.44294323270769E-09</v>
+        <v>-3.442929750028851E-09</v>
       </c>
       <c r="X2">
-        <v>-1.120163922878213E-10</v>
+        <v>-1.520420994786026E-10</v>
       </c>
       <c r="Y2">
-        <v>-7.194849109134476E-11</v>
+        <v>-5.239919349976727E-11</v>
       </c>
       <c r="Z2">
-        <v>82.8682366066229</v>
+        <v>82.86823661507249</v>
       </c>
       <c r="AA2">
-        <v>175.5922528829084</v>
+        <v>175.592252878299</v>
       </c>
       <c r="AB2">
-        <v>41.15861450991542</v>
+        <v>41.15861451669438</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>-4.394724257727977</v>
+        <v>-4.394724262341223</v>
       </c>
       <c r="AE2">
-        <v>-138.8560581246315</v>
+        <v>-138.8560581178478</v>
       </c>
       <c r="AG2">
-        <v>0.9771571746118858</v>
+        <v>0.9771571744622001</v>
       </c>
       <c r="AH2">
-        <v>0.5670703897192441</v>
+        <v>0.5670703897616893</v>
       </c>
       <c r="AI2">
-        <v>0.4671236746561608</v>
+        <v>0.4671236747580726</v>
       </c>
       <c r="AJ2">
-        <v>1.312059303119413</v>
+        <v>1.312059303014114</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -5446,16 +5446,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-8.244114005362498</v>
+        <v>-8.244114002097477</v>
       </c>
       <c r="AN2">
-        <v>-170.424970466132</v>
+        <v>-170.4249704756445</v>
       </c>
       <c r="AO2">
-        <v>132.0550451212195</v>
+        <v>132.0550451194006</v>
       </c>
       <c r="AP2">
-        <v>-12.52501517096528</v>
+        <v>-12.52501517175904</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -5613,130 +5613,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003789893398648859</v>
+        <v>0.0003789893397133099</v>
       </c>
       <c r="C2">
-        <v>1.382386873780986</v>
+        <v>1.38238687377562</v>
       </c>
       <c r="D2">
-        <v>1.177072767591246</v>
+        <v>1.177072767631418</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.382520063780011</v>
+        <v>1.382520063774493</v>
       </c>
       <c r="G2">
-        <v>1.176705138538377</v>
+        <v>1.176705138578718</v>
       </c>
       <c r="H2">
-        <v>0.004376191947819809</v>
+        <v>0.00437619194606956</v>
       </c>
       <c r="I2">
-        <v>15.96242867403315</v>
+        <v>15.96242867397119</v>
       </c>
       <c r="J2">
-        <v>13.59166558449168</v>
+        <v>13.59166558495555</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15.96396661966896</v>
+        <v>15.96396661960524</v>
       </c>
       <c r="M2">
-        <v>13.58742056983895</v>
+        <v>13.58742057030477</v>
       </c>
       <c r="N2">
-        <v>0.0006411997665621717</v>
+        <v>0.0006411997652768999</v>
       </c>
       <c r="O2">
-        <v>11.98351855471838</v>
+        <v>11.98351855468657</v>
       </c>
       <c r="P2">
-        <v>7.741742056743241</v>
+        <v>7.741742057382508</v>
       </c>
       <c r="Q2">
-        <v>-7.965710653863748E-10</v>
+        <v>-7.965728759154395E-10</v>
       </c>
       <c r="R2">
-        <v>-9.556808632887599</v>
+        <v>-9.556808632810082</v>
       </c>
       <c r="S2">
-        <v>-6.923174913857236</v>
+        <v>-6.923174914331274</v>
       </c>
       <c r="T2">
-        <v>-0.004569102559714454</v>
+        <v>-0.004569102557871039</v>
       </c>
       <c r="U2">
-        <v>9.557683332401105</v>
+        <v>9.557683332230376</v>
       </c>
       <c r="V2">
-        <v>9.294480387446209</v>
+        <v>9.29448038810933</v>
       </c>
       <c r="W2">
-        <v>-1.179888532661998E-09</v>
+        <v>-1.17987736417106E-09</v>
       </c>
       <c r="X2">
-        <v>-9.556808636121579</v>
+        <v>-9.556808636044519</v>
       </c>
       <c r="Y2">
-        <v>-6.923174918219622</v>
+        <v>-6.92317491869656</v>
       </c>
       <c r="Z2">
-        <v>79.62745686771338</v>
+        <v>79.62745688181907</v>
       </c>
       <c r="AA2">
-        <v>-169.8047984131065</v>
+        <v>-169.8047984149823</v>
       </c>
       <c r="AB2">
-        <v>65.56563408976174</v>
+        <v>65.56563409077675</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.20990687721812</v>
+        <v>10.20990687533794</v>
       </c>
       <c r="AE2">
-        <v>-114.4388495709002</v>
+        <v>-114.4388495698874</v>
       </c>
       <c r="AG2">
-        <v>1.054312579886487</v>
+        <v>1.054312579850192</v>
       </c>
       <c r="AH2">
-        <v>0.9602680458704608</v>
+        <v>0.9602680458659609</v>
       </c>
       <c r="AI2">
-        <v>0.8899836711446657</v>
+        <v>0.8899836711818816</v>
       </c>
       <c r="AJ2">
-        <v>1.158599621314868</v>
+        <v>1.158599621280886</v>
       </c>
       <c r="AK2">
-        <v>0.8466171789202198</v>
+        <v>0.8466171789167518</v>
       </c>
       <c r="AL2">
-        <v>0.7205817918579971</v>
+        <v>0.7205817918827836</v>
       </c>
       <c r="AM2">
-        <v>-2.3841729444911</v>
+        <v>-2.384172943009899</v>
       </c>
       <c r="AN2">
-        <v>-131.2300202096287</v>
+        <v>-131.2300202119293</v>
       </c>
       <c r="AO2">
-        <v>115.7733745756458</v>
+        <v>115.7733745763445</v>
       </c>
       <c r="AP2">
-        <v>-4.827878725380695</v>
+        <v>-4.82787872450255</v>
       </c>
       <c r="AQ2">
-        <v>-124.7900931130821</v>
+        <v>-124.7900931149609</v>
       </c>
       <c r="AR2">
-        <v>110.5611504471421</v>
+        <v>110.5611504481669</v>
       </c>
     </row>
   </sheetData>
@@ -5888,130 +5888,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0003789893398648859</v>
+        <v>0.0003789893397134378</v>
       </c>
       <c r="C2">
-        <v>1.382386873780986</v>
+        <v>1.382386873775621</v>
       </c>
       <c r="D2">
-        <v>1.177072767591246</v>
+        <v>1.177072767631418</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.382520063780011</v>
+        <v>1.382520063774494</v>
       </c>
       <c r="G2">
-        <v>1.176705138538377</v>
+        <v>1.176705138578717</v>
       </c>
       <c r="H2">
-        <v>0.004376191947819809</v>
+        <v>0.004376191946071036</v>
       </c>
       <c r="I2">
-        <v>15.96242867403315</v>
+        <v>15.9624286739712</v>
       </c>
       <c r="J2">
-        <v>13.59166558449168</v>
+        <v>13.59166558495554</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>15.96396661966896</v>
+        <v>15.96396661960525</v>
       </c>
       <c r="M2">
-        <v>13.58742056983895</v>
+        <v>13.58742057030476</v>
       </c>
       <c r="N2">
-        <v>0.0006411997665621717</v>
+        <v>0.0006411997652718055</v>
       </c>
       <c r="O2">
-        <v>11.98351855471838</v>
+        <v>11.98351855468658</v>
       </c>
       <c r="P2">
-        <v>7.741742056743241</v>
+        <v>7.741742057382505</v>
       </c>
       <c r="Q2">
-        <v>-7.965710653863748E-10</v>
+        <v>-7.96564672778144E-10</v>
       </c>
       <c r="R2">
-        <v>-9.556808632887599</v>
+        <v>-9.556808632810077</v>
       </c>
       <c r="S2">
-        <v>-6.923174913857236</v>
+        <v>-6.923174914331272</v>
       </c>
       <c r="T2">
-        <v>-0.004569102559714454</v>
+        <v>-0.004569102557873325</v>
       </c>
       <c r="U2">
-        <v>9.557683332401105</v>
+        <v>9.557683332230384</v>
       </c>
       <c r="V2">
-        <v>9.294480387446209</v>
+        <v>9.29448038810933</v>
       </c>
       <c r="W2">
-        <v>-1.179888532661998E-09</v>
+        <v>-1.1798780570275E-09</v>
       </c>
       <c r="X2">
-        <v>-9.556808636121579</v>
+        <v>-9.556808636044524</v>
       </c>
       <c r="Y2">
-        <v>-6.923174918219622</v>
+        <v>-6.923174918696557</v>
       </c>
       <c r="Z2">
-        <v>79.62745686771338</v>
+        <v>79.62745688188565</v>
       </c>
       <c r="AA2">
-        <v>-169.8047984131065</v>
+        <v>-169.8047984149823</v>
       </c>
       <c r="AB2">
-        <v>65.56563408976174</v>
+        <v>65.56563409077675</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>10.20990687721812</v>
+        <v>10.20990687533792</v>
       </c>
       <c r="AE2">
-        <v>-114.4388495709002</v>
+        <v>-114.4388495698874</v>
       </c>
       <c r="AG2">
-        <v>1.054312579886487</v>
+        <v>1.054312579850192</v>
       </c>
       <c r="AH2">
-        <v>0.9602680458704608</v>
+        <v>0.9602680458659607</v>
       </c>
       <c r="AI2">
-        <v>0.8899836711446657</v>
+        <v>0.8899836711818816</v>
       </c>
       <c r="AJ2">
-        <v>1.158599621314868</v>
+        <v>1.158599621280886</v>
       </c>
       <c r="AK2">
-        <v>0.8466171789202198</v>
+        <v>0.8466171789167514</v>
       </c>
       <c r="AL2">
-        <v>0.7205817918579971</v>
+        <v>0.7205817918827836</v>
       </c>
       <c r="AM2">
-        <v>-2.3841729444911</v>
+        <v>-2.384172943009904</v>
       </c>
       <c r="AN2">
-        <v>-131.2300202096287</v>
+        <v>-131.2300202119293</v>
       </c>
       <c r="AO2">
-        <v>115.7733745756458</v>
+        <v>115.7733745763445</v>
       </c>
       <c r="AP2">
-        <v>-4.827878725380695</v>
+        <v>-4.827878724502551</v>
       </c>
       <c r="AQ2">
-        <v>-124.7900931130821</v>
+        <v>-124.7900931149609</v>
       </c>
       <c r="AR2">
-        <v>110.5611504471421</v>
+        <v>110.5611504481669</v>
       </c>
     </row>
   </sheetData>
@@ -6163,106 +6163,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.00110576007688644</v>
+        <v>0.001105760076695653</v>
       </c>
       <c r="C2">
-        <v>3.921331579265833</v>
+        <v>3.921331579344982</v>
       </c>
       <c r="D2">
-        <v>2.491992615656311</v>
+        <v>2.49199261564569</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.921619255640976</v>
+        <v>3.921619255719991</v>
       </c>
       <c r="G2">
-        <v>2.491243992221614</v>
+        <v>2.491243992211113</v>
       </c>
       <c r="H2">
-        <v>0.01276821756099055</v>
+        <v>0.01276821755878753</v>
       </c>
       <c r="I2">
-        <v>45.27963685741819</v>
+        <v>45.27963685833212</v>
       </c>
       <c r="J2">
-        <v>28.77505214935461</v>
+        <v>28.77505214923198</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45.28295865807075</v>
+        <v>45.28295865898313</v>
       </c>
       <c r="M2">
-        <v>28.76640779052373</v>
+        <v>28.76640779040249</v>
       </c>
       <c r="N2">
-        <v>-0.0001657479216687773</v>
+        <v>-0.0001657479220666588</v>
       </c>
       <c r="O2">
-        <v>30.31563093572613</v>
+        <v>30.31563093839077</v>
       </c>
       <c r="P2">
-        <v>-0.1080137611974396</v>
+        <v>-0.1080137610617768</v>
       </c>
       <c r="Q2">
-        <v>-4.732833175599518E-09</v>
+        <v>-4.73284047232546E-09</v>
       </c>
       <c r="R2">
-        <v>-1.865520605788879E-10</v>
+        <v>-1.70161485954228E-10</v>
       </c>
       <c r="S2">
-        <v>-3.135278361381313E-11</v>
+        <v>-2.61366535783582E-11</v>
       </c>
       <c r="T2">
-        <v>-0.01215427143801855</v>
+        <v>-0.01215427143489471</v>
       </c>
       <c r="U2">
-        <v>1.849625464593171</v>
+        <v>1.849625463434005</v>
       </c>
       <c r="V2">
-        <v>12.13153435979691</v>
+        <v>12.13153436159197</v>
       </c>
       <c r="W2">
-        <v>-2.245511132637127E-09</v>
+        <v>-2.245497374332828E-09</v>
       </c>
       <c r="X2">
-        <v>-2.388679217592195E-10</v>
+        <v>-1.937003854173848E-10</v>
       </c>
       <c r="Y2">
-        <v>-1.389787981594198E-10</v>
+        <v>-1.618392096625691E-10</v>
       </c>
       <c r="Z2">
-        <v>84.60874107099022</v>
+        <v>84.60874107370827</v>
       </c>
       <c r="AA2">
-        <v>-170.319391012681</v>
+        <v>-170.3193910145042</v>
       </c>
       <c r="AB2">
-        <v>37.22943984433548</v>
+        <v>37.22943984769437</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.696208666296528</v>
+        <v>9.696208664470612</v>
       </c>
       <c r="AE2">
-        <v>-142.7892737939802</v>
+        <v>-142.789273790618</v>
       </c>
       <c r="AG2">
-        <v>0.9520045754588131</v>
+        <v>0.9520045753788619</v>
       </c>
       <c r="AH2">
-        <v>0.6707651729349149</v>
+        <v>0.6707651729785564</v>
       </c>
       <c r="AI2">
-        <v>0.4216157503531273</v>
+        <v>0.4216157504172618</v>
       </c>
       <c r="AJ2">
-        <v>1.31505683285586</v>
+        <v>1.315056832820254</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6271,16 +6271,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-6.172553620115819</v>
+        <v>-6.172553619473832</v>
       </c>
       <c r="AN2">
-        <v>-166.827973406101</v>
+        <v>-166.827973410413</v>
       </c>
       <c r="AO2">
-        <v>127.739562384195</v>
+        <v>127.7395623868377</v>
       </c>
       <c r="AP2">
-        <v>-8.930089727480206</v>
+        <v>-8.930089728364202</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -6357,52 +6357,52 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.309686024628783</v>
+        <v>1.309686024628784</v>
       </c>
       <c r="C2">
-        <v>1.309686024628783</v>
+        <v>1.309686024628784</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.837059479583174</v>
+        <v>2.837059479583173</v>
       </c>
       <c r="F2">
-        <v>45.36885473239911</v>
+        <v>45.36885473239914</v>
       </c>
       <c r="G2">
-        <v>45.36885473239911</v>
+        <v>45.36885473239914</v>
       </c>
       <c r="H2">
-        <v>28.40499517047036</v>
+        <v>28.40499517047038</v>
       </c>
       <c r="I2">
-        <v>-25.72916224161305</v>
+        <v>-25.72916224161306</v>
       </c>
       <c r="J2">
-        <v>28.76520341755291</v>
+        <v>28.76520341755293</v>
       </c>
       <c r="K2">
-        <v>-25.72916225404873</v>
+        <v>-25.72916225404875</v>
       </c>
       <c r="L2">
-        <v>-54.52967391402493</v>
+        <v>-54.52967391402492</v>
       </c>
       <c r="M2">
         <v>125.4703260859678</v>
       </c>
       <c r="N2">
-        <v>0.8910570420386134</v>
+        <v>0.8910570420386132</v>
       </c>
       <c r="O2">
-        <v>0.8020156209364413</v>
+        <v>0.802015620936441</v>
       </c>
       <c r="P2">
-        <v>-9.168679204911147</v>
+        <v>-9.16867920491114</v>
       </c>
       <c r="Q2">
-        <v>-9.529673900180356</v>
+        <v>-9.529673900180343</v>
       </c>
     </row>
   </sheetData>
@@ -6554,106 +6554,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.00110576007688644</v>
+        <v>0.001105760076695653</v>
       </c>
       <c r="C2">
-        <v>3.921331579265833</v>
+        <v>3.921331579344982</v>
       </c>
       <c r="D2">
-        <v>2.491992615656311</v>
+        <v>2.49199261564569</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.921619255640976</v>
+        <v>3.921619255719991</v>
       </c>
       <c r="G2">
-        <v>2.491243992221614</v>
+        <v>2.491243992211113</v>
       </c>
       <c r="H2">
-        <v>0.01276821756099055</v>
+        <v>0.01276821755878753</v>
       </c>
       <c r="I2">
-        <v>45.27963685741819</v>
+        <v>45.27963685833212</v>
       </c>
       <c r="J2">
-        <v>28.77505214935461</v>
+        <v>28.77505214923198</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>45.28295865807075</v>
+        <v>45.28295865898313</v>
       </c>
       <c r="M2">
-        <v>28.76640779052373</v>
+        <v>28.76640779040249</v>
       </c>
       <c r="N2">
-        <v>-0.0001657479216687773</v>
+        <v>-0.0001657479220666588</v>
       </c>
       <c r="O2">
-        <v>30.31563093572613</v>
+        <v>30.31563093839077</v>
       </c>
       <c r="P2">
-        <v>-0.1080137611974396</v>
+        <v>-0.1080137610617768</v>
       </c>
       <c r="Q2">
-        <v>-4.732833175599518E-09</v>
+        <v>-4.73284047232546E-09</v>
       </c>
       <c r="R2">
-        <v>-1.865520605788879E-10</v>
+        <v>-1.70161485954228E-10</v>
       </c>
       <c r="S2">
-        <v>-3.135278361381313E-11</v>
+        <v>-2.61366535783582E-11</v>
       </c>
       <c r="T2">
-        <v>-0.01215427143801855</v>
+        <v>-0.01215427143489471</v>
       </c>
       <c r="U2">
-        <v>1.849625464593171</v>
+        <v>1.849625463434005</v>
       </c>
       <c r="V2">
-        <v>12.13153435979691</v>
+        <v>12.13153436159197</v>
       </c>
       <c r="W2">
-        <v>-2.245511132637127E-09</v>
+        <v>-2.245497374332828E-09</v>
       </c>
       <c r="X2">
-        <v>-2.388679217592195E-10</v>
+        <v>-1.937003854173848E-10</v>
       </c>
       <c r="Y2">
-        <v>-1.389787981594198E-10</v>
+        <v>-1.618392096625691E-10</v>
       </c>
       <c r="Z2">
-        <v>84.60874107099022</v>
+        <v>84.60874107370827</v>
       </c>
       <c r="AA2">
-        <v>-170.319391012681</v>
+        <v>-170.3193910145042</v>
       </c>
       <c r="AB2">
-        <v>37.22943984433548</v>
+        <v>37.22943984769437</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>9.696208666296528</v>
+        <v>9.696208664470612</v>
       </c>
       <c r="AE2">
-        <v>-142.7892737939802</v>
+        <v>-142.789273790618</v>
       </c>
       <c r="AG2">
-        <v>0.9520045754588131</v>
+        <v>0.9520045753788619</v>
       </c>
       <c r="AH2">
-        <v>0.6707651729349149</v>
+        <v>0.6707651729785564</v>
       </c>
       <c r="AI2">
-        <v>0.4216157503531273</v>
+        <v>0.4216157504172618</v>
       </c>
       <c r="AJ2">
-        <v>1.31505683285586</v>
+        <v>1.315056832820254</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6662,16 +6662,16 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-6.172553620115819</v>
+        <v>-6.172553619473832</v>
       </c>
       <c r="AN2">
-        <v>-166.827973406101</v>
+        <v>-166.827973410413</v>
       </c>
       <c r="AO2">
-        <v>127.739562384195</v>
+        <v>127.7395623868377</v>
       </c>
       <c r="AP2">
-        <v>-8.930089727480206</v>
+        <v>-8.930089728364202</v>
       </c>
       <c r="AQ2">
         <v>0</v>
@@ -6829,130 +6829,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004965920590055564</v>
+        <v>0.0004965920588805776</v>
       </c>
       <c r="C2">
-        <v>1.210481473118725</v>
+        <v>1.210481473120173</v>
       </c>
       <c r="D2">
-        <v>0.9669780958370113</v>
+        <v>0.9669780958584732</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.210751047387656</v>
+        <v>1.210751047388998</v>
       </c>
       <c r="G2">
-        <v>0.9664867208349793</v>
+        <v>0.9664867208565686</v>
       </c>
       <c r="H2">
-        <v>0.005734151178885771</v>
+        <v>0.00573415117744264</v>
       </c>
       <c r="I2">
-        <v>13.97743608708302</v>
+        <v>13.97743608709973</v>
       </c>
       <c r="J2">
-        <v>11.16570127863941</v>
+        <v>11.16570127888722</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>13.98054886261769</v>
+        <v>13.98054886263319</v>
       </c>
       <c r="M2">
-        <v>11.16002736884548</v>
+        <v>11.16002736909477</v>
       </c>
       <c r="N2">
-        <v>0.001401849078759649</v>
+        <v>0.001401849078109864</v>
       </c>
       <c r="O2">
-        <v>10.45747396767881</v>
+        <v>10.45747396777075</v>
       </c>
       <c r="P2">
-        <v>5.683293932461228</v>
+        <v>5.683293932823799</v>
       </c>
       <c r="Q2">
-        <v>-1.535268163034217E-09</v>
+        <v>-1.53527579544118E-09</v>
       </c>
       <c r="R2">
-        <v>-7.329590493907329</v>
+        <v>-7.329590493926487</v>
       </c>
       <c r="S2">
-        <v>-4.670482906607187</v>
+        <v>-4.67048290681562</v>
       </c>
       <c r="T2">
-        <v>-0.005370939819061215</v>
+        <v>-0.005370939817609201</v>
       </c>
       <c r="U2">
-        <v>6.607602902022703</v>
+        <v>6.607602901932867</v>
       </c>
       <c r="V2">
-        <v>7.062655713054262</v>
+        <v>7.062655713418974</v>
       </c>
       <c r="W2">
-        <v>-1.285328211739992E-09</v>
+        <v>-1.285324745069804E-09</v>
       </c>
       <c r="X2">
-        <v>-7.329590495891582</v>
+        <v>-7.329590495905516</v>
       </c>
       <c r="Y2">
-        <v>-4.670482910331748</v>
+        <v>-4.670482910540717</v>
       </c>
       <c r="Z2">
-        <v>72.99237596486938</v>
+        <v>72.99237596856375</v>
       </c>
       <c r="AA2">
-        <v>-164.1397217050114</v>
+        <v>-164.1397217064079</v>
       </c>
       <c r="AB2">
-        <v>64.68196303285482</v>
+        <v>64.68196303406836</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>15.88001650219275</v>
+        <v>15.88001650079237</v>
       </c>
       <c r="AE2">
-        <v>-115.3222920059518</v>
+        <v>-115.3222920047384</v>
       </c>
       <c r="AG2">
-        <v>0.9680371888032221</v>
+        <v>0.9680371887732189</v>
       </c>
       <c r="AH2">
-        <v>0.885004373904601</v>
+        <v>0.8850043739056701</v>
       </c>
       <c r="AI2">
-        <v>0.8118943814214227</v>
+        <v>0.811894381449208</v>
       </c>
       <c r="AJ2">
-        <v>1.119236804481869</v>
+        <v>1.11923680445655</v>
       </c>
       <c r="AK2">
-        <v>0.7414305680261327</v>
+        <v>0.7414305680269846</v>
       </c>
       <c r="AL2">
-        <v>0.591849827396307</v>
+        <v>0.5918498274095334</v>
       </c>
       <c r="AM2">
-        <v>-2.379415652553714</v>
+        <v>-2.379415651563932</v>
       </c>
       <c r="AN2">
-        <v>-131.852789126914</v>
+        <v>-131.8527891288897</v>
       </c>
       <c r="AO2">
-        <v>115.8584531965948</v>
+        <v>115.8584531974682</v>
       </c>
       <c r="AP2">
-        <v>-5.99254479675426</v>
+        <v>-5.992544796450702</v>
       </c>
       <c r="AQ2">
-        <v>-119.1199834900463</v>
+        <v>-119.1199834914671</v>
       </c>
       <c r="AR2">
-        <v>109.6777080168848</v>
+        <v>109.6777080181015</v>
       </c>
     </row>
   </sheetData>
@@ -7104,130 +7104,130 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>0.0004965920590055564</v>
+        <v>0.0004965920588805776</v>
       </c>
       <c r="C2">
-        <v>1.210481473118725</v>
+        <v>1.210481473120173</v>
       </c>
       <c r="D2">
-        <v>0.9669780958370113</v>
+        <v>0.9669780958584732</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1.210751047387656</v>
+        <v>1.210751047388998</v>
       </c>
       <c r="G2">
-        <v>0.9664867208349793</v>
+        <v>0.9664867208565686</v>
       </c>
       <c r="H2">
-        <v>0.005734151178885771</v>
+        <v>0.00573415117744264</v>
       </c>
       <c r="I2">
-        <v>13.97743608708302</v>
+        <v>13.97743608709973</v>
       </c>
       <c r="J2">
-        <v>11.16570127863941</v>
+        <v>11.16570127888722</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>13.98054886261769</v>
+        <v>13.98054886263319</v>
       </c>
       <c r="M2">
-        <v>11.16002736884548</v>
+        <v>11.16002736909477</v>
       </c>
       <c r="N2">
-        <v>0.001401849078759649</v>
+        <v>0.001401849078109864</v>
       </c>
       <c r="O2">
-        <v>10.45747396767881</v>
+        <v>10.45747396777075</v>
       </c>
       <c r="P2">
-        <v>5.683293932461228</v>
+        <v>5.683293932823799</v>
       </c>
       <c r="Q2">
-        <v>-1.535268163034217E-09</v>
+        <v>-1.53527579544118E-09</v>
       </c>
       <c r="R2">
-        <v>-7.329590493907329</v>
+        <v>-7.329590493926487</v>
       </c>
       <c r="S2">
-        <v>-4.670482906607187</v>
+        <v>-4.67048290681562</v>
       </c>
       <c r="T2">
-        <v>-0.005370939819061215</v>
+        <v>-0.005370939817609201</v>
       </c>
       <c r="U2">
-        <v>6.607602902022703</v>
+        <v>6.607602901932867</v>
       </c>
       <c r="V2">
-        <v>7.062655713054262</v>
+        <v>7.062655713418974</v>
       </c>
       <c r="W2">
-        <v>-1.285328211739992E-09</v>
+        <v>-1.285324745069804E-09</v>
       </c>
       <c r="X2">
-        <v>-7.329590495891582</v>
+        <v>-7.329590495905516</v>
       </c>
       <c r="Y2">
-        <v>-4.670482910331748</v>
+        <v>-4.670482910540717</v>
       </c>
       <c r="Z2">
-        <v>72.99237596486938</v>
+        <v>72.99237596856375</v>
       </c>
       <c r="AA2">
-        <v>-164.1397217050114</v>
+        <v>-164.1397217064079</v>
       </c>
       <c r="AB2">
-        <v>64.68196303285482</v>
+        <v>64.68196303406836</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>15.88001650219275</v>
+        <v>15.88001650079237</v>
       </c>
       <c r="AE2">
-        <v>-115.3222920059518</v>
+        <v>-115.3222920047384</v>
       </c>
       <c r="AG2">
-        <v>0.9680371888032221</v>
+        <v>0.9680371887732189</v>
       </c>
       <c r="AH2">
-        <v>0.885004373904601</v>
+        <v>0.8850043739056701</v>
       </c>
       <c r="AI2">
-        <v>0.8118943814214227</v>
+        <v>0.811894381449208</v>
       </c>
       <c r="AJ2">
-        <v>1.119236804481869</v>
+        <v>1.11923680445655</v>
       </c>
       <c r="AK2">
-        <v>0.7414305680261327</v>
+        <v>0.7414305680269846</v>
       </c>
       <c r="AL2">
-        <v>0.591849827396307</v>
+        <v>0.5918498274095334</v>
       </c>
       <c r="AM2">
-        <v>-2.379415652553714</v>
+        <v>-2.379415651563932</v>
       </c>
       <c r="AN2">
-        <v>-131.852789126914</v>
+        <v>-131.8527891288897</v>
       </c>
       <c r="AO2">
-        <v>115.8584531965948</v>
+        <v>115.8584531974682</v>
       </c>
       <c r="AP2">
-        <v>-5.99254479675426</v>
+        <v>-5.992544796450702</v>
       </c>
       <c r="AQ2">
-        <v>-119.1199834900463</v>
+        <v>-119.1199834914671</v>
       </c>
       <c r="AR2">
-        <v>109.6777080168848</v>
+        <v>109.6777080181015</v>
       </c>
     </row>
   </sheetData>
@@ -7307,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2.837059479583175</v>
+        <v>2.837059479583173</v>
       </c>
       <c r="F2">
         <v>45.36885473239911</v>
@@ -7316,31 +7316,31 @@
         <v>45.36885473239911</v>
       </c>
       <c r="H2">
-        <v>28.40499517047034</v>
+        <v>28.40499517047036</v>
       </c>
       <c r="I2">
-        <v>-25.72916224161303</v>
+        <v>-25.72916224161305</v>
       </c>
       <c r="J2">
-        <v>28.76520341755294</v>
+        <v>28.76520341755292</v>
       </c>
       <c r="K2">
-        <v>-25.72916225404877</v>
+        <v>-25.72916225404875</v>
       </c>
       <c r="L2">
-        <v>-54.52967391402498</v>
+        <v>-54.52967391402493</v>
       </c>
       <c r="M2">
-        <v>125.4703260859677</v>
+        <v>125.4703260859678</v>
       </c>
       <c r="N2">
-        <v>0.8910570420386137</v>
+        <v>0.8910570420386135</v>
       </c>
       <c r="O2">
         <v>0.8020156209364414</v>
       </c>
       <c r="P2">
-        <v>-9.16867920491114</v>
+        <v>-9.168679204911136</v>
       </c>
       <c r="Q2">
         <v>-9.52967390018034</v>
@@ -7414,16 +7414,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="C2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.838062054648196</v>
+        <v>6.838062054648194</v>
       </c>
       <c r="F2">
         <v>124.7634330090034</v>
@@ -7432,31 +7432,31 @@
         <v>124.7634330090034</v>
       </c>
       <c r="H2">
-        <v>38.85252268584023</v>
+        <v>38.85252268584024</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>22.95972360762209</v>
+        <v>22.95972360762206</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-69.67231644738079</v>
+        <v>-69.67231644738078</v>
       </c>
       <c r="M2">
         <v>110.3276835526119</v>
       </c>
       <c r="N2">
-        <v>0.3617201835011319</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-39.09154322526811</v>
+        <v>-39.09154322526815</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -7530,16 +7530,16 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="C2">
-        <v>3.601610081638499</v>
+        <v>3.601610081638498</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6.838062054648196</v>
+        <v>6.838062054648194</v>
       </c>
       <c r="F2">
         <v>124.7634330090034</v>
@@ -7548,31 +7548,31 @@
         <v>124.7634330090034</v>
       </c>
       <c r="H2">
-        <v>38.85252268584023</v>
+        <v>38.85252268584024</v>
       </c>
       <c r="I2">
         <v>-1E-07</v>
       </c>
       <c r="J2">
-        <v>22.95972360762209</v>
+        <v>22.95972360762206</v>
       </c>
       <c r="K2">
         <v>-1E-07</v>
       </c>
       <c r="L2">
-        <v>-69.67231644738079</v>
+        <v>-69.67231644738078</v>
       </c>
       <c r="M2">
         <v>110.3276835526119</v>
       </c>
       <c r="N2">
-        <v>0.3617201835011319</v>
+        <v>0.361720183501132</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>-39.09154322526811</v>
+        <v>-39.09154322526815</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -7646,10 +7646,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="C2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7664,34 +7664,34 @@
         <v>39.70717444103497</v>
       </c>
       <c r="H2">
-        <v>23.64358897071033</v>
+        <v>23.64358897071036</v>
       </c>
       <c r="I2">
-        <v>-19.70824627309613</v>
+        <v>-19.70824627309617</v>
       </c>
       <c r="J2">
-        <v>22.03381935746363</v>
+        <v>22.0338193574636</v>
       </c>
       <c r="K2">
-        <v>-19.70824628278311</v>
+        <v>-19.70824628278309</v>
       </c>
       <c r="L2">
-        <v>-52.63434508457839</v>
+        <v>-52.63434508457834</v>
       </c>
       <c r="M2">
-        <v>127.3656549154143</v>
+        <v>127.3656549154144</v>
       </c>
       <c r="N2">
-        <v>0.8139299031165275</v>
+        <v>0.8139299031165274</v>
       </c>
       <c r="O2">
         <v>0.7019303077896069</v>
       </c>
       <c r="P2">
-        <v>-9.652735617430418</v>
+        <v>-9.652735617430428</v>
       </c>
       <c r="Q2">
-        <v>-7.634345070499235</v>
+        <v>-7.634345070499253</v>
       </c>
     </row>
   </sheetData>
@@ -7762,10 +7762,10 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="C2">
-        <v>1.146247392614548</v>
+        <v>1.146247392614549</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -7780,34 +7780,34 @@
         <v>39.70717444103497</v>
       </c>
       <c r="H2">
-        <v>23.64358897071033</v>
+        <v>23.64358897071036</v>
       </c>
       <c r="I2">
-        <v>-19.70824627309613</v>
+        <v>-19.70824627309617</v>
       </c>
       <c r="J2">
-        <v>22.03381935746363</v>
+        <v>22.0338193574636</v>
       </c>
       <c r="K2">
-        <v>-19.70824628278311</v>
+        <v>-19.70824628278309</v>
       </c>
       <c r="L2">
-        <v>-52.63434508457839</v>
+        <v>-52.63434508457834</v>
       </c>
       <c r="M2">
-        <v>127.3656549154143</v>
+        <v>127.3656549154144</v>
       </c>
       <c r="N2">
-        <v>0.8139299031165275</v>
+        <v>0.8139299031165274</v>
       </c>
       <c r="O2">
         <v>0.7019303077896069</v>
       </c>
       <c r="P2">
-        <v>-9.652735617430418</v>
+        <v>-9.652735617430428</v>
       </c>
       <c r="Q2">
-        <v>-7.634345070499235</v>
+        <v>-7.634345070499253</v>
       </c>
     </row>
   </sheetData>
@@ -7959,127 +7959,127 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>3.709154423746197</v>
+        <v>3.709154423744979</v>
       </c>
       <c r="D2">
-        <v>3.709154423746191</v>
+        <v>3.709154423744982</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>3.709154423746193</v>
+        <v>3.709154423744977</v>
       </c>
       <c r="G2">
-        <v>3.709154423746191</v>
+        <v>3.709154423744981</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>42.82962610031516</v>
+        <v>42.8296261003011</v>
       </c>
       <c r="J2">
-        <v>42.8296261003151</v>
+        <v>42.82962610030113</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>42.82962610031511</v>
+        <v>42.82962610030108</v>
       </c>
       <c r="M2">
-        <v>42.8296261003151</v>
+        <v>42.82962610030112</v>
       </c>
       <c r="N2">
-        <v>-1.563194052542763E-14</v>
+        <v>-5.210646841809227E-15</v>
       </c>
       <c r="O2">
-        <v>30.17661447772734</v>
+        <v>30.17661447772221</v>
       </c>
       <c r="P2">
-        <v>-15.86847458187111</v>
+        <v>-15.86847458187514</v>
       </c>
       <c r="Q2">
-        <v>-1.5631940525427E-14</v>
+        <v>-5.210646841809276E-15</v>
       </c>
       <c r="R2">
-        <v>-23.02254452973994</v>
+        <v>-23.02254452973953</v>
       </c>
       <c r="S2">
-        <v>23.02254452985859</v>
+        <v>23.02254452985797</v>
       </c>
       <c r="T2">
-        <v>-5.210646841807091E-15</v>
+        <v>-5.210646841809326E-15</v>
       </c>
       <c r="U2">
-        <v>3.130989834145738</v>
+        <v>3.130989834187397</v>
       </c>
       <c r="V2">
-        <v>13.10324558048884</v>
+        <v>13.10324558045219</v>
       </c>
       <c r="W2">
-        <v>1.904117332321756E-27</v>
+        <v>-5.001102148442347E-29</v>
       </c>
       <c r="X2">
-        <v>4.986127873181712</v>
+        <v>4.986127873134728</v>
       </c>
       <c r="Y2">
-        <v>-4.986127873161449</v>
+        <v>-4.98612787313009</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-167.7798457937229</v>
+        <v>-167.7798457937528</v>
       </c>
       <c r="AB2">
-        <v>12.22015420626987</v>
+        <v>12.22015420623993</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>12.22015420626988</v>
+        <v>12.22015420623993</v>
       </c>
       <c r="AE2">
-        <v>-167.7798457937229</v>
+        <v>-167.7798457937528</v>
       </c>
       <c r="AF2">
-        <v>1.100000023834231</v>
+        <v>1.10000002383429</v>
       </c>
       <c r="AG2">
-        <v>0.7083556674756124</v>
+        <v>0.7083556674758259</v>
       </c>
       <c r="AH2">
-        <v>0.4804898682207091</v>
+        <v>0.4804898682203932</v>
       </c>
       <c r="AI2">
-        <v>1.100000023834231</v>
+        <v>1.10000002383429</v>
       </c>
       <c r="AJ2">
-        <v>0.5500000119158659</v>
+        <v>0.5500000119158046</v>
       </c>
       <c r="AK2">
-        <v>0.5500000119184737</v>
+        <v>0.5500000119184838</v>
       </c>
       <c r="AL2">
-        <v>-6.989567673226516E-12</v>
+        <v>5.487565486616769E-13</v>
       </c>
       <c r="AM2">
-        <v>-161.8562887546769</v>
+        <v>-161.8562887546276</v>
       </c>
       <c r="AN2">
-        <v>152.6722796269069</v>
+        <v>152.6722796269628</v>
       </c>
       <c r="AO2">
-        <v>-6.979164657278612E-12</v>
+        <v>5.499164589708564E-13</v>
       </c>
       <c r="AP2">
-        <v>179.9999999998726</v>
+        <v>179.9999999999541</v>
       </c>
       <c r="AQ2">
-        <v>179.9999999999818</v>
+        <v>-179.9999999999593</v>
       </c>
     </row>
   </sheetData>
